--- a/data/tables/table_id_vs_rest_analysis.xlsx
+++ b/data/tables/table_id_vs_rest_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="273">
   <si>
     <t>Cassa</t>
   </si>
@@ -47,6 +47,9 @@
     <t>odds_ratio_pretty</t>
   </si>
   <si>
+    <t>99.0% CI</t>
+  </si>
+  <si>
     <t>p_value</t>
   </si>
   <si>
@@ -143,6 +146,63 @@
     <t>OR = 0.967</t>
   </si>
   <si>
+    <t>[0.843, 3.287]</t>
+  </si>
+  <si>
+    <t>[0.952, 0.991]</t>
+  </si>
+  <si>
+    <t>[-2.177, 0.543]</t>
+  </si>
+  <si>
+    <t>[0.331, 0.410]</t>
+  </si>
+  <si>
+    <t>[-0.012, 0.528]</t>
+  </si>
+  <si>
+    <t>[-0.135, -0.120]</t>
+  </si>
+  <si>
+    <t>[-1.383, 0.637]</t>
+  </si>
+  <si>
+    <t>[0.220, 0.278]</t>
+  </si>
+  <si>
+    <t>[0.649, 3.461]</t>
+  </si>
+  <si>
+    <t>[0.943, 0.990]</t>
+  </si>
+  <si>
+    <t>[1.024, 5.852]</t>
+  </si>
+  <si>
+    <t>[0.952, 0.990]</t>
+  </si>
+  <si>
+    <t>[-4.943, -1.349]</t>
+  </si>
+  <si>
+    <t>[0.326, 0.402]</t>
+  </si>
+  <si>
+    <t>[-0.068, 0.644]</t>
+  </si>
+  <si>
+    <t>[-2.368, 0.340]</t>
+  </si>
+  <si>
+    <t>[0.215, 0.272]</t>
+  </si>
+  <si>
+    <t>[0.261, 2.607]</t>
+  </si>
+  <si>
+    <t>[0.944, 0.991]</t>
+  </si>
+  <si>
     <t>childlessness</t>
   </si>
   <si>
@@ -248,6 +308,57 @@
     <t>OR = 1.060</t>
   </si>
   <si>
+    <t>[0.989, 1.231]</t>
+  </si>
+  <si>
+    <t>[-0.568, -0.130]</t>
+  </si>
+  <si>
+    <t>[0.327, 0.407]</t>
+  </si>
+  <si>
+    <t>[0.014, 0.101]</t>
+  </si>
+  <si>
+    <t>[-0.134, -0.119]</t>
+  </si>
+  <si>
+    <t>[-0.279, 0.044]</t>
+  </si>
+  <si>
+    <t>[0.219, 0.278]</t>
+  </si>
+  <si>
+    <t>[0.905, 1.189]</t>
+  </si>
+  <si>
+    <t>[0.941, 0.989]</t>
+  </si>
+  <si>
+    <t>[1.036, 1.434]</t>
+  </si>
+  <si>
+    <t>[0.950, 0.988]</t>
+  </si>
+  <si>
+    <t>[-0.846, -0.178]</t>
+  </si>
+  <si>
+    <t>[0.326, 0.404]</t>
+  </si>
+  <si>
+    <t>[0.042, 0.175]</t>
+  </si>
+  <si>
+    <t>[-0.510, 0.012]</t>
+  </si>
+  <si>
+    <t>[0.216, 0.273]</t>
+  </si>
+  <si>
+    <t>[0.862, 1.303]</t>
+  </si>
+  <si>
     <t>OR = 1.783</t>
   </si>
   <si>
@@ -284,6 +395,51 @@
     <t>OR = 1.009</t>
   </si>
   <si>
+    <t>[1.011, 3.144]</t>
+  </si>
+  <si>
+    <t>[0.954, 0.992]</t>
+  </si>
+  <si>
+    <t>[-1.695, 0.567]</t>
+  </si>
+  <si>
+    <t>[0.331, 0.409]</t>
+  </si>
+  <si>
+    <t>[-0.112, 0.337]</t>
+  </si>
+  <si>
+    <t>[-1.206, 0.460]</t>
+  </si>
+  <si>
+    <t>[0.728, 2.949]</t>
+  </si>
+  <si>
+    <t>[0.945, 0.992]</t>
+  </si>
+  <si>
+    <t>[0.948, 3.908]</t>
+  </si>
+  <si>
+    <t>[0.952, 0.989]</t>
+  </si>
+  <si>
+    <t>[-3.950, -1.055]</t>
+  </si>
+  <si>
+    <t>[0.326, 0.403]</t>
+  </si>
+  <si>
+    <t>[-0.154, 0.420]</t>
+  </si>
+  <si>
+    <t>[-1.769, 0.443]</t>
+  </si>
+  <si>
+    <t>[0.406, 2.508]</t>
+  </si>
+  <si>
     <t>OR = 1.422</t>
   </si>
   <si>
@@ -318,6 +474,54 @@
   </si>
   <si>
     <t>OR = 1.463</t>
+  </si>
+  <si>
+    <t>[0.866, 2.333]</t>
+  </si>
+  <si>
+    <t>[0.953, 0.991]</t>
+  </si>
+  <si>
+    <t>[-2.086, -0.106]</t>
+  </si>
+  <si>
+    <t>[0.325, 0.402]</t>
+  </si>
+  <si>
+    <t>[0.065, 0.457]</t>
+  </si>
+  <si>
+    <t>[-1.014, 0.407]</t>
+  </si>
+  <si>
+    <t>[0.217, 0.274]</t>
+  </si>
+  <si>
+    <t>[0.638, 2.191]</t>
+  </si>
+  <si>
+    <t>[1.200, 6.331]</t>
+  </si>
+  <si>
+    <t>[-5.620, -2.242]</t>
+  </si>
+  <si>
+    <t>[0.325, 0.401]</t>
+  </si>
+  <si>
+    <t>[0.211, 0.882]</t>
+  </si>
+  <si>
+    <t>[-2.737, -0.103]</t>
+  </si>
+  <si>
+    <t>[0.216, 0.272]</t>
+  </si>
+  <si>
+    <t>[0.512, 4.176]</t>
+  </si>
+  <si>
+    <t>[0.944, 0.990]</t>
   </si>
   <si>
     <t>Info</t>
@@ -987,10 +1191,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI23"/>
+  <dimension ref="A1:BM23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:61">
+    <row r="1" spans="1:65">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1009,10 +1213,10 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
@@ -1026,11 +1230,11 @@
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AG1" s="1"/>
-      <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
@@ -1043,12 +1247,12 @@
       <c r="AR1" s="1"/>
       <c r="AS1" s="1"/>
       <c r="AT1" s="1"/>
-      <c r="AU1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="AU1" s="1"/>
       <c r="AV1" s="1"/>
       <c r="AW1" s="1"/>
-      <c r="AX1" s="1"/>
+      <c r="AX1" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="AY1" s="1"/>
       <c r="AZ1" s="1"/>
       <c r="BA1" s="1"/>
@@ -1060,8 +1264,12 @@
       <c r="BG1" s="1"/>
       <c r="BH1" s="1"/>
       <c r="BI1" s="1"/>
+      <c r="BJ1" s="1"/>
+      <c r="BK1" s="1"/>
+      <c r="BL1" s="1"/>
+      <c r="BM1" s="1"/>
     </row>
-    <row r="2" spans="1:61">
+    <row r="2" spans="1:65">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>4</v>
@@ -1109,148 +1317,160 @@
         <v>18</v>
       </c>
       <c r="Q2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AA2" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="AB2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AD2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AF2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AG2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AI2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AJ2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AK2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AL2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AM2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AN2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AO2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="AN2" s="1" t="s">
+      <c r="AP2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AO2" s="1" t="s">
+      <c r="AQ2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AP2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="AQ2" s="1" t="s">
+      <c r="AR2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AR2" s="1" t="s">
+      <c r="AT2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AS2" s="1" t="s">
+      <c r="AU2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AT2" s="1" t="s">
+      <c r="AV2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AU2" s="1" t="s">
+      <c r="AW2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AX2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="AV2" s="1" t="s">
+      <c r="AY2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AW2" s="1" t="s">
+      <c r="AZ2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="AX2" s="1" t="s">
+      <c r="BA2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AY2" s="1" t="s">
+      <c r="BB2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AZ2" s="1" t="s">
+      <c r="BC2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="BA2" s="1" t="s">
+      <c r="BD2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="BB2" s="1" t="s">
+      <c r="BE2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="BC2" s="1" t="s">
+      <c r="BF2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="BD2" s="1" t="s">
+      <c r="BG2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="BE2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="BF2" s="1" t="s">
+      <c r="BH2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="BI2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="BG2" s="1" t="s">
+      <c r="BJ2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="BH2" s="1" t="s">
+      <c r="BK2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="BI2" s="1" t="s">
+      <c r="BL2" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="BM2" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="3" spans="1:61" hidden="1"/>
-    <row r="4" spans="1:61">
+    <row r="3" spans="1:65" hidden="1"/>
+    <row r="4" spans="1:65">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4">
         <v>0.5093222047276087</v>
@@ -1265,177 +1485,189 @@
         <v>3.286968940864523</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4">
         <v>0.05391982810800325</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>0.7548775935120455</v>
       </c>
-      <c r="J4">
-        <v>14</v>
-      </c>
       <c r="K4">
+        <v>14</v>
+      </c>
+      <c r="L4">
         <v>357033</v>
       </c>
-      <c r="L4" t="s">
-        <v>42</v>
-      </c>
       <c r="M4" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="N4" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="O4" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="P4" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="Q4" t="s">
-        <v>19</v>
-      </c>
-      <c r="R4">
+        <v>80</v>
+      </c>
+      <c r="R4" t="s">
+        <v>20</v>
+      </c>
+      <c r="S4">
         <v>0.09839490847431284</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>1.103398440475535</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>0.9889403034990167</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>1.231103752305564</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
+        <v>82</v>
+      </c>
+      <c r="X4" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y4">
+        <v>0.02065372200597305</v>
+      </c>
+      <c r="Z4">
+        <v>0.2891521080836227</v>
+      </c>
+      <c r="AA4">
+        <v>14</v>
+      </c>
+      <c r="AB4">
+        <v>344184</v>
+      </c>
+      <c r="AC4" t="s">
         <v>62</v>
       </c>
-      <c r="W4">
-        <v>0.02065372200597305</v>
-      </c>
-      <c r="X4">
-        <v>0.2891521080836227</v>
-      </c>
-      <c r="Y4">
-        <v>14</v>
-      </c>
-      <c r="Z4">
-        <v>344184</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>48</v>
-      </c>
       <c r="AD4" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AE4" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="AF4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG4">
+        <v>70</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI4">
         <v>0.5780360873653451</v>
       </c>
-      <c r="AH4">
+      <c r="AJ4">
         <v>1.782534249389257</v>
       </c>
-      <c r="AI4">
+      <c r="AK4">
         <v>1.010664033486562</v>
       </c>
-      <c r="AJ4">
+      <c r="AL4">
         <v>3.143901677478631</v>
       </c>
-      <c r="AK4" t="s">
-        <v>77</v>
-      </c>
-      <c r="AL4">
+      <c r="AM4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>126</v>
+      </c>
+      <c r="AO4">
         <v>0.008690833921798246</v>
       </c>
-      <c r="AM4">
+      <c r="AP4">
         <v>0.1216716749051754</v>
       </c>
-      <c r="AN4">
-        <v>14</v>
-      </c>
-      <c r="AO4">
+      <c r="AQ4">
+        <v>14</v>
+      </c>
+      <c r="AR4">
         <v>357686</v>
       </c>
-      <c r="AP4" t="s">
-        <v>42</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>48</v>
-      </c>
       <c r="AS4" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="AT4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="AU4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AV4">
+        <v>68</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>20</v>
+      </c>
+      <c r="AY4">
         <v>0.351722749162467</v>
       </c>
-      <c r="AW4">
+      <c r="AZ4">
         <v>1.421514353034082</v>
       </c>
-      <c r="AX4">
+      <c r="BA4">
         <v>0.8661271065115037</v>
       </c>
-      <c r="AY4">
+      <c r="BB4">
         <v>2.333032924025069</v>
       </c>
-      <c r="AZ4" t="s">
-        <v>89</v>
-      </c>
-      <c r="BA4">
+      <c r="BC4" t="s">
+        <v>141</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>153</v>
+      </c>
+      <c r="BE4">
         <v>0.06745817374348981</v>
       </c>
-      <c r="BB4">
+      <c r="BF4">
         <v>0.9444144324088573</v>
       </c>
-      <c r="BC4">
-        <v>14</v>
-      </c>
-      <c r="BD4">
+      <c r="BG4">
+        <v>14</v>
+      </c>
+      <c r="BH4">
         <v>369265</v>
       </c>
-      <c r="BE4" t="s">
-        <v>42</v>
-      </c>
-      <c r="BF4" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG4" t="s">
-        <v>48</v>
-      </c>
-      <c r="BH4" t="s">
-        <v>50</v>
-      </c>
       <c r="BI4" t="s">
-        <v>60</v>
+        <v>62</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>68</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>70</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:61">
+    <row r="5" spans="1:65">
       <c r="A5" s="1">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5">
         <v>-0.02889898293689634</v>
@@ -1450,177 +1682,189 @@
         <v>0.9909147879303888</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5">
         <v>0.0001666728133605025</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>0.002333419387047036</v>
       </c>
-      <c r="J5">
-        <v>14</v>
-      </c>
       <c r="K5">
+        <v>14</v>
+      </c>
+      <c r="L5">
         <v>357033</v>
       </c>
-      <c r="L5" t="s">
-        <v>42</v>
-      </c>
       <c r="M5" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="N5" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="O5" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="P5" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="Q5" t="s">
-        <v>20</v>
-      </c>
-      <c r="R5">
+        <v>80</v>
+      </c>
+      <c r="R5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S5">
         <v>-0.02883535203430651</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>0.9715764193790846</v>
       </c>
-      <c r="T5">
+      <c r="U5">
         <v>0.9522090694782707</v>
       </c>
-      <c r="U5">
+      <c r="V5">
         <v>0.9913376893277153</v>
       </c>
-      <c r="V5" t="s">
-        <v>23</v>
-      </c>
-      <c r="W5">
+      <c r="W5" t="s">
+        <v>24</v>
+      </c>
+      <c r="X5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y5">
         <v>0.0002253217230773107</v>
       </c>
-      <c r="X5">
+      <c r="Z5">
         <v>0.003154504123082349</v>
       </c>
-      <c r="Y5">
-        <v>14</v>
-      </c>
-      <c r="Z5">
+      <c r="AA5">
+        <v>14</v>
+      </c>
+      <c r="AB5">
         <v>344184</v>
       </c>
-      <c r="AA5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>47</v>
-      </c>
       <c r="AC5" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="AD5" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AE5" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="AF5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG5">
+        <v>70</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI5">
         <v>-0.02776314972670461</v>
       </c>
-      <c r="AH5">
+      <c r="AJ5">
         <v>0.9726187045283731</v>
       </c>
-      <c r="AI5">
+      <c r="AK5">
         <v>0.953589199731478</v>
       </c>
-      <c r="AJ5">
+      <c r="AL5">
         <v>0.9920279557117802</v>
       </c>
-      <c r="AK5" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL5">
+      <c r="AM5" t="s">
+        <v>115</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>127</v>
+      </c>
+      <c r="AO5">
         <v>0.0002954697000033838</v>
       </c>
-      <c r="AM5">
+      <c r="AP5">
         <v>0.004136575800047373</v>
       </c>
-      <c r="AN5">
-        <v>14</v>
-      </c>
-      <c r="AO5">
+      <c r="AQ5">
+        <v>14</v>
+      </c>
+      <c r="AR5">
         <v>357686</v>
       </c>
-      <c r="AP5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>48</v>
-      </c>
       <c r="AS5" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="AT5" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="AU5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV5">
+        <v>68</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>80</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY5">
         <v>-0.02867680594559065</v>
       </c>
-      <c r="AW5">
+      <c r="AZ5">
         <v>0.9717304712321023</v>
       </c>
-      <c r="AX5">
+      <c r="BA5">
         <v>0.9530231886175226</v>
       </c>
-      <c r="AY5">
+      <c r="BB5">
         <v>0.9908049667613327</v>
       </c>
-      <c r="AZ5" t="s">
-        <v>23</v>
-      </c>
-      <c r="BA5">
+      <c r="BC5" t="s">
+        <v>24</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>154</v>
+      </c>
+      <c r="BE5">
         <v>0.0001447725569437376</v>
       </c>
-      <c r="BB5">
+      <c r="BF5">
         <v>0.002026815797212326</v>
       </c>
-      <c r="BC5">
-        <v>14</v>
-      </c>
-      <c r="BD5">
+      <c r="BG5">
+        <v>14</v>
+      </c>
+      <c r="BH5">
         <v>369265</v>
       </c>
-      <c r="BE5" t="s">
-        <v>42</v>
-      </c>
-      <c r="BF5" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG5" t="s">
-        <v>48</v>
-      </c>
-      <c r="BH5" t="s">
-        <v>50</v>
-      </c>
       <c r="BI5" t="s">
-        <v>60</v>
+        <v>62</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK5" t="s">
+        <v>68</v>
+      </c>
+      <c r="BL5" t="s">
+        <v>70</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:61">
+    <row r="6" spans="1:65">
       <c r="A6" s="1">
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6">
         <v>-0.8169825659729438</v>
@@ -1635,177 +1879,189 @@
         <v>1.721628578649113</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6">
         <v>0.1218462557881011</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>1.705847581033416</v>
       </c>
-      <c r="J6">
-        <v>14</v>
-      </c>
       <c r="K6">
+        <v>14</v>
+      </c>
+      <c r="L6">
         <v>355367</v>
       </c>
-      <c r="L6" t="s">
-        <v>43</v>
-      </c>
       <c r="M6" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="N6" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="O6" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="P6" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="Q6" t="s">
-        <v>19</v>
-      </c>
-      <c r="R6">
+        <v>81</v>
+      </c>
+      <c r="R6" t="s">
+        <v>20</v>
+      </c>
+      <c r="S6">
         <v>-0.3489824715002082</v>
       </c>
-      <c r="S6">
+      <c r="T6">
         <v>0.7054054948616575</v>
       </c>
-      <c r="T6">
+      <c r="U6">
         <v>0.5666954111088005</v>
       </c>
-      <c r="U6">
+      <c r="V6">
         <v>0.8780676575577312</v>
       </c>
-      <c r="V6" t="s">
+      <c r="W6" t="s">
+        <v>83</v>
+      </c>
+      <c r="X6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y6">
+        <v>4.03309014364817E-05</v>
+      </c>
+      <c r="Z6">
+        <v>0.0005646326201107437</v>
+      </c>
+      <c r="AA6">
+        <v>14</v>
+      </c>
+      <c r="AB6">
+        <v>342569</v>
+      </c>
+      <c r="AC6" t="s">
         <v>63</v>
       </c>
-      <c r="W6">
-        <v>4.03309014364817E-05</v>
-      </c>
-      <c r="X6">
-        <v>0.0005646326201107437</v>
-      </c>
-      <c r="Y6">
-        <v>14</v>
-      </c>
-      <c r="Z6">
-        <v>342569</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>48</v>
-      </c>
       <c r="AD6" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="AE6" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AF6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG6">
+        <v>71</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI6">
         <v>-0.564261608781945</v>
       </c>
-      <c r="AH6">
+      <c r="AJ6">
         <v>0.5687799738778532</v>
       </c>
-      <c r="AI6">
+      <c r="AK6">
         <v>0.1835382458961302</v>
       </c>
-      <c r="AJ6">
+      <c r="AL6">
         <v>1.762633488758391</v>
       </c>
-      <c r="AK6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL6">
+      <c r="AM6" t="s">
+        <v>116</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>128</v>
+      </c>
+      <c r="AO6">
         <v>0.19878738227783</v>
       </c>
-      <c r="AM6">
+      <c r="AP6">
         <v>2.78302335188962</v>
       </c>
-      <c r="AN6">
-        <v>14</v>
-      </c>
-      <c r="AO6">
+      <c r="AQ6">
+        <v>14</v>
+      </c>
+      <c r="AR6">
         <v>356016</v>
       </c>
-      <c r="AP6" t="s">
-        <v>43</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>48</v>
-      </c>
       <c r="AS6" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="AT6" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="AU6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AV6">
+        <v>68</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>81</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>20</v>
+      </c>
+      <c r="AY6">
         <v>-1.096313222638188</v>
       </c>
-      <c r="AW6">
+      <c r="AZ6">
         <v>0.3341005703029186</v>
       </c>
-      <c r="AX6">
+      <c r="BA6">
         <v>0.124135265000924</v>
       </c>
-      <c r="AY6">
+      <c r="BB6">
         <v>0.8992061287008537</v>
       </c>
-      <c r="AZ6" t="s">
-        <v>90</v>
-      </c>
-      <c r="BA6">
+      <c r="BC6" t="s">
+        <v>142</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>155</v>
+      </c>
+      <c r="BE6">
         <v>0.004341261532529528</v>
       </c>
-      <c r="BB6">
+      <c r="BF6">
         <v>0.0607776614554134</v>
       </c>
-      <c r="BC6">
-        <v>14</v>
-      </c>
-      <c r="BD6">
+      <c r="BG6">
+        <v>14</v>
+      </c>
+      <c r="BH6">
         <v>367562</v>
       </c>
-      <c r="BE6" t="s">
-        <v>43</v>
-      </c>
-      <c r="BF6" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG6" t="s">
-        <v>48</v>
-      </c>
-      <c r="BH6" t="s">
-        <v>51</v>
-      </c>
       <c r="BI6" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK6" t="s">
+        <v>68</v>
+      </c>
+      <c r="BL6" t="s">
+        <v>71</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:61">
+    <row r="7" spans="1:65">
       <c r="A7" s="1">
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7">
         <v>0.3703950937419732</v>
@@ -1820,177 +2076,189 @@
         <v>1.506196047220818</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7">
+        <v>26</v>
+      </c>
+      <c r="H7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7">
         <v>6.796937316863805E-131</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>9.515712243609327E-130</v>
       </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
       <c r="K7">
+        <v>14</v>
+      </c>
+      <c r="L7">
         <v>355367</v>
       </c>
-      <c r="L7" t="s">
-        <v>43</v>
-      </c>
       <c r="M7" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="N7" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="O7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="P7" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="Q7" t="s">
-        <v>20</v>
-      </c>
-      <c r="R7">
+        <v>81</v>
+      </c>
+      <c r="R7" t="s">
+        <v>21</v>
+      </c>
+      <c r="S7">
         <v>0.3668111843990907</v>
       </c>
-      <c r="S7">
+      <c r="T7">
         <v>1.443125408797638</v>
       </c>
-      <c r="T7">
+      <c r="U7">
         <v>1.386651943440575</v>
       </c>
-      <c r="U7">
+      <c r="V7">
         <v>1.501898840129957</v>
       </c>
-      <c r="V7" t="s">
-        <v>64</v>
-      </c>
-      <c r="W7">
+      <c r="W7" t="s">
+        <v>84</v>
+      </c>
+      <c r="X7" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y7">
         <v>7.52445487119093E-124</v>
       </c>
-      <c r="X7">
+      <c r="Z7">
         <v>1.05342368196673E-122</v>
       </c>
-      <c r="Y7">
-        <v>14</v>
-      </c>
-      <c r="Z7">
+      <c r="AA7">
+        <v>14</v>
+      </c>
+      <c r="AB7">
         <v>342569</v>
       </c>
-      <c r="AA7" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>47</v>
-      </c>
       <c r="AC7" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="AD7" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="AE7" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AF7" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG7">
+        <v>71</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI7">
         <v>0.3701067406190353</v>
       </c>
-      <c r="AH7">
+      <c r="AJ7">
         <v>1.447889155000011</v>
       </c>
-      <c r="AI7">
+      <c r="AK7">
         <v>1.392281711814432</v>
       </c>
-      <c r="AJ7">
+      <c r="AL7">
         <v>1.505717547948414</v>
       </c>
-      <c r="AK7" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL7">
+      <c r="AM7" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>129</v>
+      </c>
+      <c r="AO7">
         <v>6.91399733568495E-131</v>
       </c>
-      <c r="AM7">
+      <c r="AP7">
         <v>9.67959626995893E-130</v>
       </c>
-      <c r="AN7">
-        <v>14</v>
-      </c>
-      <c r="AO7">
+      <c r="AQ7">
+        <v>14</v>
+      </c>
+      <c r="AR7">
         <v>356016</v>
       </c>
-      <c r="AP7" t="s">
-        <v>43</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>48</v>
-      </c>
       <c r="AS7" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="AT7" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="AU7" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV7">
+        <v>68</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>71</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>81</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY7">
         <v>0.3634053767569774</v>
       </c>
-      <c r="AW7">
+      <c r="AZ7">
         <v>1.438218761543083</v>
       </c>
-      <c r="AX7">
+      <c r="BA7">
         <v>1.383856384703043</v>
       </c>
-      <c r="AY7">
+      <c r="BB7">
         <v>1.494716669243382</v>
       </c>
-      <c r="AZ7" t="s">
-        <v>91</v>
-      </c>
-      <c r="BA7">
+      <c r="BC7" t="s">
+        <v>143</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>156</v>
+      </c>
+      <c r="BE7">
         <v>2.281497904206718E-130</v>
       </c>
-      <c r="BB7">
+      <c r="BF7">
         <v>3.194097065889405E-129</v>
       </c>
-      <c r="BC7">
-        <v>14</v>
-      </c>
-      <c r="BD7">
+      <c r="BG7">
+        <v>14</v>
+      </c>
+      <c r="BH7">
         <v>367562</v>
       </c>
-      <c r="BE7" t="s">
-        <v>43</v>
-      </c>
-      <c r="BF7" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG7" t="s">
-        <v>48</v>
-      </c>
-      <c r="BH7" t="s">
-        <v>51</v>
-      </c>
       <c r="BI7" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="BJ7" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK7" t="s">
+        <v>68</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>71</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:61">
+    <row r="8" spans="1:65">
       <c r="A8" s="1">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8">
         <v>0.2578868517674528</v>
@@ -2005,177 +2273,189 @@
         <v>1.695042882111916</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8">
+        <v>27</v>
+      </c>
+      <c r="H8" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8">
         <v>0.01382035835109129</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>0.193485016915278</v>
       </c>
-      <c r="J8">
-        <v>14</v>
-      </c>
       <c r="K8">
+        <v>14</v>
+      </c>
+      <c r="L8">
         <v>358742</v>
       </c>
-      <c r="L8" t="s">
-        <v>44</v>
-      </c>
       <c r="M8" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="N8" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="O8" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="P8" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="Q8" t="s">
-        <v>19</v>
-      </c>
-      <c r="R8">
+        <v>81</v>
+      </c>
+      <c r="R8" t="s">
+        <v>20</v>
+      </c>
+      <c r="S8">
         <v>0.05752746635760921</v>
       </c>
-      <c r="S8">
+      <c r="T8">
         <v>1.059214363015679</v>
       </c>
-      <c r="T8">
+      <c r="U8">
         <v>1.01418524385181</v>
       </c>
-      <c r="U8">
+      <c r="V8">
         <v>1.106242743739471</v>
       </c>
-      <c r="V8" t="s">
-        <v>65</v>
-      </c>
-      <c r="W8">
+      <c r="W8" t="s">
+        <v>85</v>
+      </c>
+      <c r="X8" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y8">
         <v>0.0006472158753572436</v>
       </c>
-      <c r="X8">
+      <c r="Z8">
         <v>0.009061022255001411</v>
       </c>
-      <c r="Y8">
-        <v>14</v>
-      </c>
-      <c r="Z8">
+      <c r="AA8">
+        <v>14</v>
+      </c>
+      <c r="AB8">
         <v>345837</v>
       </c>
-      <c r="AA8" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>47</v>
-      </c>
       <c r="AC8" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="AD8" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="AE8" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AF8" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG8">
+        <v>72</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI8">
         <v>0.1122491628933242</v>
       </c>
-      <c r="AH8">
+      <c r="AJ8">
         <v>1.118791587268348</v>
       </c>
-      <c r="AI8">
+      <c r="AK8">
         <v>0.8937573691755251</v>
       </c>
-      <c r="AJ8">
+      <c r="AL8">
         <v>1.400485924828899</v>
       </c>
-      <c r="AK8" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL8">
+      <c r="AM8" t="s">
+        <v>117</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>130</v>
+      </c>
+      <c r="AO8">
         <v>0.1979190212454155</v>
       </c>
-      <c r="AM8">
+      <c r="AP8">
         <v>2.770866297435817</v>
       </c>
-      <c r="AN8">
-        <v>14</v>
-      </c>
-      <c r="AO8">
+      <c r="AQ8">
+        <v>14</v>
+      </c>
+      <c r="AR8">
         <v>359400</v>
       </c>
-      <c r="AP8" t="s">
-        <v>44</v>
-      </c>
-      <c r="AQ8" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR8" t="s">
-        <v>48</v>
-      </c>
       <c r="AS8" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="AT8" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="AU8" t="s">
-        <v>19</v>
-      </c>
-      <c r="AV8">
+        <v>68</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>81</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AY8">
         <v>0.2610785441443073</v>
       </c>
-      <c r="AW8">
+      <c r="AZ8">
         <v>1.298329637619394</v>
       </c>
-      <c r="AX8">
+      <c r="BA8">
         <v>1.066865477641125</v>
       </c>
-      <c r="AY8">
+      <c r="BB8">
         <v>1.580011616504788</v>
       </c>
-      <c r="AZ8" t="s">
-        <v>92</v>
-      </c>
-      <c r="BA8">
+      <c r="BC8" t="s">
+        <v>144</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>157</v>
+      </c>
+      <c r="BE8">
         <v>0.0006150011806460767</v>
       </c>
-      <c r="BB8">
+      <c r="BF8">
         <v>0.008610016529045073</v>
       </c>
-      <c r="BC8">
-        <v>14</v>
-      </c>
-      <c r="BD8">
+      <c r="BG8">
+        <v>14</v>
+      </c>
+      <c r="BH8">
         <v>371041</v>
       </c>
-      <c r="BE8" t="s">
-        <v>44</v>
-      </c>
-      <c r="BF8" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG8" t="s">
-        <v>48</v>
-      </c>
-      <c r="BH8" t="s">
-        <v>52</v>
-      </c>
       <c r="BI8" t="s">
-        <v>61</v>
+        <v>64</v>
+      </c>
+      <c r="BJ8" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK8" t="s">
+        <v>68</v>
+      </c>
+      <c r="BL8" t="s">
+        <v>72</v>
+      </c>
+      <c r="BM8" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:61">
+    <row r="9" spans="1:65">
       <c r="A9" s="1">
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9">
         <v>-0.12733914993154</v>
@@ -2190,177 +2470,189 @@
         <v>0.8873113197844862</v>
       </c>
       <c r="G9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>48</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K9">
+        <v>14</v>
+      </c>
+      <c r="L9">
         <v>358742</v>
       </c>
-      <c r="L9" t="s">
-        <v>44</v>
-      </c>
       <c r="M9" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="N9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O9" t="s">
+        <v>68</v>
+      </c>
+      <c r="P9" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>81</v>
+      </c>
+      <c r="R9" t="s">
+        <v>21</v>
+      </c>
+      <c r="S9">
+        <v>-0.1265468179069989</v>
+      </c>
+      <c r="T9">
+        <v>0.8811328957798473</v>
+      </c>
+      <c r="U9">
+        <v>0.8741776402934687</v>
+      </c>
+      <c r="V9">
+        <v>0.888143489651299</v>
+      </c>
+      <c r="W9" t="s">
+        <v>28</v>
+      </c>
+      <c r="X9" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>14</v>
+      </c>
+      <c r="AB9">
+        <v>345837</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI9">
+        <v>-0.1274564182301577</v>
+      </c>
+      <c r="AJ9">
+        <v>0.8803317814152776</v>
+      </c>
+      <c r="AK9">
+        <v>0.8735154437543104</v>
+      </c>
+      <c r="AL9">
+        <v>0.8872013092739001</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>28</v>
+      </c>
+      <c r="AN9" t="s">
         <v>48</v>
       </c>
-      <c r="O9" t="s">
-        <v>52</v>
-      </c>
-      <c r="P9" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>20</v>
-      </c>
-      <c r="R9">
-        <v>-0.1265468179069989</v>
-      </c>
-      <c r="S9">
-        <v>0.8811328957798473</v>
-      </c>
-      <c r="T9">
-        <v>0.8741776402934687</v>
-      </c>
-      <c r="U9">
-        <v>0.888143489651299</v>
-      </c>
-      <c r="V9" t="s">
-        <v>27</v>
-      </c>
-      <c r="W9">
+      <c r="AO9">
         <v>0</v>
       </c>
-      <c r="X9">
+      <c r="AP9">
         <v>0</v>
       </c>
-      <c r="Y9">
-        <v>14</v>
-      </c>
-      <c r="Z9">
-        <v>345837</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC9" t="s">
+      <c r="AQ9">
+        <v>14</v>
+      </c>
+      <c r="AR9">
+        <v>359400</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>81</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY9">
+        <v>-0.1276413807921878</v>
+      </c>
+      <c r="AZ9">
+        <v>0.8801689680512031</v>
+      </c>
+      <c r="BA9">
+        <v>0.8734624263881977</v>
+      </c>
+      <c r="BB9">
+        <v>0.8869270032870501</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>38</v>
+      </c>
+      <c r="BD9" t="s">
         <v>48</v>
       </c>
-      <c r="AD9" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG9">
-        <v>-0.1274564182301577</v>
-      </c>
-      <c r="AH9">
-        <v>0.8803317814152776</v>
-      </c>
-      <c r="AI9">
-        <v>0.8735154437543104</v>
-      </c>
-      <c r="AJ9">
-        <v>0.8872013092739001</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>27</v>
-      </c>
-      <c r="AL9">
+      <c r="BE9">
         <v>0</v>
       </c>
-      <c r="AM9">
+      <c r="BF9">
         <v>0</v>
       </c>
-      <c r="AN9">
-        <v>14</v>
-      </c>
-      <c r="AO9">
-        <v>359400</v>
-      </c>
-      <c r="AP9" t="s">
-        <v>44</v>
-      </c>
-      <c r="AQ9" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>48</v>
-      </c>
-      <c r="AS9" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT9" t="s">
-        <v>61</v>
-      </c>
-      <c r="AU9" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV9">
-        <v>-0.1276413807921878</v>
-      </c>
-      <c r="AW9">
-        <v>0.8801689680512031</v>
-      </c>
-      <c r="AX9">
-        <v>0.8734624263881977</v>
-      </c>
-      <c r="AY9">
-        <v>0.8869270032870501</v>
-      </c>
-      <c r="AZ9" t="s">
-        <v>37</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>0</v>
-      </c>
-      <c r="BC9">
-        <v>14</v>
-      </c>
-      <c r="BD9">
+      <c r="BG9">
+        <v>14</v>
+      </c>
+      <c r="BH9">
         <v>371041</v>
       </c>
-      <c r="BE9" t="s">
-        <v>44</v>
-      </c>
-      <c r="BF9" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG9" t="s">
-        <v>48</v>
-      </c>
-      <c r="BH9" t="s">
-        <v>52</v>
-      </c>
       <c r="BI9" t="s">
-        <v>61</v>
+        <v>64</v>
+      </c>
+      <c r="BJ9" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK9" t="s">
+        <v>68</v>
+      </c>
+      <c r="BL9" t="s">
+        <v>72</v>
+      </c>
+      <c r="BM9" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="10" spans="1:61">
+    <row r="10" spans="1:65">
       <c r="A10" s="1">
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10">
         <v>-0.3727679225793313</v>
@@ -2375,177 +2667,189 @@
         <v>1.891640251821604</v>
       </c>
       <c r="G10" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10">
+        <v>29</v>
+      </c>
+      <c r="H10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I10">
         <v>0.3418684040844706</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>4.786157657182589</v>
       </c>
-      <c r="J10">
-        <v>14</v>
-      </c>
       <c r="K10">
+        <v>14</v>
+      </c>
+      <c r="L10">
         <v>114900</v>
       </c>
-      <c r="L10" t="s">
-        <v>45</v>
-      </c>
       <c r="M10" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="N10" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="O10" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="P10" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="Q10" t="s">
-        <v>19</v>
-      </c>
-      <c r="R10">
+        <v>81</v>
+      </c>
+      <c r="R10" t="s">
+        <v>20</v>
+      </c>
+      <c r="S10">
         <v>-0.1174685900868903</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <v>0.8891684400112743</v>
       </c>
-      <c r="T10">
+      <c r="U10">
         <v>0.7563175640007664</v>
       </c>
-      <c r="U10">
+      <c r="V10">
         <v>1.04535522159483</v>
       </c>
-      <c r="V10" t="s">
-        <v>66</v>
-      </c>
-      <c r="W10">
+      <c r="W10" t="s">
+        <v>86</v>
+      </c>
+      <c r="X10" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y10">
         <v>0.06151330403233402</v>
       </c>
-      <c r="X10">
+      <c r="Z10">
         <v>0.8611862564526763</v>
       </c>
-      <c r="Y10">
-        <v>14</v>
-      </c>
-      <c r="Z10">
+      <c r="AA10">
+        <v>14</v>
+      </c>
+      <c r="AB10">
         <v>110697</v>
       </c>
-      <c r="AA10" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>47</v>
-      </c>
       <c r="AC10" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AD10" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="AE10" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AF10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG10">
+        <v>73</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI10">
         <v>-0.3731601619861405</v>
       </c>
-      <c r="AH10">
+      <c r="AJ10">
         <v>0.6885549436847788</v>
       </c>
-      <c r="AI10">
+      <c r="AK10">
         <v>0.2992978762571878</v>
       </c>
-      <c r="AJ10">
+      <c r="AL10">
         <v>1.584067071913821</v>
       </c>
-      <c r="AK10" t="s">
-        <v>28</v>
-      </c>
-      <c r="AL10">
+      <c r="AM10" t="s">
+        <v>29</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>131</v>
+      </c>
+      <c r="AO10">
         <v>0.2486305499385038</v>
       </c>
-      <c r="AM10">
+      <c r="AP10">
         <v>3.480827699139053</v>
       </c>
-      <c r="AN10">
-        <v>14</v>
-      </c>
-      <c r="AO10">
+      <c r="AQ10">
+        <v>14</v>
+      </c>
+      <c r="AR10">
         <v>115115</v>
       </c>
-      <c r="AP10" t="s">
-        <v>45</v>
-      </c>
-      <c r="AQ10" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR10" t="s">
-        <v>48</v>
-      </c>
       <c r="AS10" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AT10" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="AU10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AV10">
+        <v>68</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>20</v>
+      </c>
+      <c r="AY10">
         <v>-0.3037028920121826</v>
       </c>
-      <c r="AW10">
+      <c r="AZ10">
         <v>0.7380801233777908</v>
       </c>
-      <c r="AX10">
+      <c r="BA10">
         <v>0.3627462419677221</v>
       </c>
-      <c r="AY10">
+      <c r="BB10">
         <v>1.501772328695411</v>
       </c>
-      <c r="AZ10" t="s">
-        <v>93</v>
-      </c>
-      <c r="BA10">
+      <c r="BC10" t="s">
+        <v>145</v>
+      </c>
+      <c r="BD10" t="s">
+        <v>158</v>
+      </c>
+      <c r="BE10">
         <v>0.2707785971728013</v>
       </c>
-      <c r="BB10">
+      <c r="BF10">
         <v>3.790900360419218</v>
       </c>
-      <c r="BC10">
-        <v>14</v>
-      </c>
-      <c r="BD10">
+      <c r="BG10">
+        <v>14</v>
+      </c>
+      <c r="BH10">
         <v>118911</v>
       </c>
-      <c r="BE10" t="s">
-        <v>45</v>
-      </c>
-      <c r="BF10" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG10" t="s">
-        <v>48</v>
-      </c>
-      <c r="BH10" t="s">
-        <v>53</v>
-      </c>
       <c r="BI10" t="s">
-        <v>61</v>
+        <v>65</v>
+      </c>
+      <c r="BJ10" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK10" t="s">
+        <v>68</v>
+      </c>
+      <c r="BL10" t="s">
+        <v>73</v>
+      </c>
+      <c r="BM10" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:61">
+    <row r="11" spans="1:65">
       <c r="A11" s="1">
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11">
         <v>0.2486456128905995</v>
@@ -2560,177 +2864,189 @@
         <v>1.319892087348232</v>
       </c>
       <c r="G11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11">
+        <v>30</v>
+      </c>
+      <c r="H11" t="s">
+        <v>50</v>
+      </c>
+      <c r="I11">
         <v>8.696559831143453E-109</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>1.217518376360083E-107</v>
       </c>
-      <c r="J11">
-        <v>14</v>
-      </c>
       <c r="K11">
+        <v>14</v>
+      </c>
+      <c r="L11">
         <v>114900</v>
       </c>
-      <c r="L11" t="s">
-        <v>45</v>
-      </c>
       <c r="M11" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="N11" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="O11" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="P11" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="Q11" t="s">
-        <v>20</v>
-      </c>
-      <c r="R11">
+        <v>81</v>
+      </c>
+      <c r="R11" t="s">
+        <v>21</v>
+      </c>
+      <c r="S11">
         <v>0.2487185631106028</v>
       </c>
-      <c r="S11">
+      <c r="T11">
         <v>1.282381072938256</v>
       </c>
-      <c r="T11">
+      <c r="U11">
         <v>1.245169775949933</v>
       </c>
-      <c r="U11">
+      <c r="V11">
         <v>1.32070441155359</v>
       </c>
-      <c r="V11" t="s">
-        <v>29</v>
-      </c>
-      <c r="W11">
+      <c r="W11" t="s">
+        <v>30</v>
+      </c>
+      <c r="X11" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y11">
         <v>5.995561309684663E-105</v>
       </c>
-      <c r="X11">
+      <c r="Z11">
         <v>8.393785833558527E-104</v>
       </c>
-      <c r="Y11">
-        <v>14</v>
-      </c>
-      <c r="Z11">
+      <c r="AA11">
+        <v>14</v>
+      </c>
+      <c r="AB11">
         <v>110697</v>
       </c>
-      <c r="AA11" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>47</v>
-      </c>
       <c r="AC11" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AD11" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="AE11" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AF11" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG11">
+        <v>73</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI11">
         <v>0.2493664515095481</v>
       </c>
-      <c r="AH11">
+      <c r="AJ11">
         <v>1.283212181962315</v>
       </c>
-      <c r="AI11">
+      <c r="AK11">
         <v>1.246678358909233</v>
       </c>
-      <c r="AJ11">
+      <c r="AL11">
         <v>1.320816626172278</v>
       </c>
-      <c r="AK11" t="s">
-        <v>29</v>
-      </c>
-      <c r="AL11">
+      <c r="AM11" t="s">
+        <v>30</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>50</v>
+      </c>
+      <c r="AO11">
         <v>1.464080497079297E-109</v>
       </c>
-      <c r="AM11">
+      <c r="AP11">
         <v>2.049712695911016E-108</v>
       </c>
-      <c r="AN11">
-        <v>14</v>
-      </c>
-      <c r="AO11">
+      <c r="AQ11">
+        <v>14</v>
+      </c>
+      <c r="AR11">
         <v>115115</v>
       </c>
-      <c r="AP11" t="s">
-        <v>45</v>
-      </c>
-      <c r="AQ11" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR11" t="s">
-        <v>48</v>
-      </c>
       <c r="AS11" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AT11" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="AU11" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV11">
+        <v>68</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>81</v>
+      </c>
+      <c r="AX11" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY11">
         <v>0.2450929443480978</v>
       </c>
-      <c r="AW11">
+      <c r="AZ11">
         <v>1.277740066403592</v>
       </c>
-      <c r="AX11">
+      <c r="BA11">
         <v>1.241938342866762</v>
       </c>
-      <c r="AY11">
+      <c r="BB11">
         <v>1.314573856802332</v>
       </c>
-      <c r="AZ11" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA11">
+      <c r="BC11" t="s">
+        <v>95</v>
+      </c>
+      <c r="BD11" t="s">
+        <v>159</v>
+      </c>
+      <c r="BE11">
         <v>2.506392275724875E-109</v>
       </c>
-      <c r="BB11">
+      <c r="BF11">
         <v>3.508949186014824E-108</v>
       </c>
-      <c r="BC11">
-        <v>14</v>
-      </c>
-      <c r="BD11">
+      <c r="BG11">
+        <v>14</v>
+      </c>
+      <c r="BH11">
         <v>118911</v>
       </c>
-      <c r="BE11" t="s">
-        <v>45</v>
-      </c>
-      <c r="BF11" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG11" t="s">
-        <v>48</v>
-      </c>
-      <c r="BH11" t="s">
-        <v>53</v>
-      </c>
       <c r="BI11" t="s">
-        <v>61</v>
+        <v>65</v>
+      </c>
+      <c r="BJ11" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK11" t="s">
+        <v>68</v>
+      </c>
+      <c r="BL11" t="s">
+        <v>73</v>
+      </c>
+      <c r="BM11" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:61">
+    <row r="12" spans="1:65">
       <c r="A12" s="1">
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>0.4048372496613884</v>
@@ -2745,177 +3061,189 @@
         <v>3.460624798915865</v>
       </c>
       <c r="G12" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12">
+        <v>31</v>
+      </c>
+      <c r="H12" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12">
         <v>0.2126006613366788</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>2.976409258713502</v>
       </c>
-      <c r="J12">
-        <v>14</v>
-      </c>
       <c r="K12">
+        <v>14</v>
+      </c>
+      <c r="L12">
         <v>358043</v>
       </c>
-      <c r="L12" t="s">
-        <v>46</v>
-      </c>
       <c r="M12" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="N12" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="O12" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="P12" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="Q12" t="s">
-        <v>19</v>
-      </c>
-      <c r="R12">
+        <v>80</v>
+      </c>
+      <c r="R12" t="s">
+        <v>20</v>
+      </c>
+      <c r="S12">
         <v>0.03642177563985358</v>
       </c>
-      <c r="S12">
+      <c r="T12">
         <v>1.037093174894636</v>
       </c>
-      <c r="T12">
+      <c r="U12">
         <v>0.9049039071809443</v>
       </c>
-      <c r="U12">
+      <c r="V12">
         <v>1.188592783032339</v>
       </c>
-      <c r="V12" t="s">
-        <v>67</v>
-      </c>
-      <c r="W12">
+      <c r="W12" t="s">
+        <v>87</v>
+      </c>
+      <c r="X12" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y12">
         <v>0.4914128364189262</v>
       </c>
-      <c r="X12">
+      <c r="Z12">
         <v>6.879779709864967</v>
       </c>
-      <c r="Y12">
-        <v>14</v>
-      </c>
-      <c r="Z12">
+      <c r="AA12">
+        <v>14</v>
+      </c>
+      <c r="AB12">
         <v>345147</v>
       </c>
-      <c r="AA12" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>47</v>
-      </c>
       <c r="AC12" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AD12" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="AE12" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="AF12" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG12">
+        <v>74</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI12">
         <v>0.3817439986536102</v>
       </c>
-      <c r="AH12">
+      <c r="AJ12">
         <v>1.464837036874897</v>
       </c>
-      <c r="AI12">
+      <c r="AK12">
         <v>0.7275285118716347</v>
       </c>
-      <c r="AJ12">
+      <c r="AL12">
         <v>2.94936557067749</v>
       </c>
-      <c r="AK12" t="s">
-        <v>81</v>
-      </c>
-      <c r="AL12">
+      <c r="AM12" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>132</v>
+      </c>
+      <c r="AO12">
         <v>0.1600112403864515</v>
       </c>
-      <c r="AM12">
+      <c r="AP12">
         <v>2.240157365410322</v>
       </c>
-      <c r="AN12">
-        <v>14</v>
-      </c>
-      <c r="AO12">
+      <c r="AQ12">
+        <v>14</v>
+      </c>
+      <c r="AR12">
         <v>358700</v>
       </c>
-      <c r="AP12" t="s">
-        <v>46</v>
-      </c>
-      <c r="AQ12" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR12" t="s">
-        <v>48</v>
-      </c>
       <c r="AS12" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="AT12" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="AU12" t="s">
-        <v>19</v>
-      </c>
-      <c r="AV12">
+        <v>68</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>80</v>
+      </c>
+      <c r="AX12" t="s">
+        <v>20</v>
+      </c>
+      <c r="AY12">
         <v>0.1674357035690579</v>
       </c>
-      <c r="AW12">
+      <c r="AZ12">
         <v>1.182269272046495</v>
       </c>
-      <c r="AX12">
+      <c r="BA12">
         <v>0.6379054537436841</v>
       </c>
-      <c r="AY12">
+      <c r="BB12">
         <v>2.19117209834513</v>
       </c>
-      <c r="AZ12" t="s">
-        <v>94</v>
-      </c>
-      <c r="BA12">
+      <c r="BC12" t="s">
+        <v>146</v>
+      </c>
+      <c r="BD12" t="s">
+        <v>160</v>
+      </c>
+      <c r="BE12">
         <v>0.4845498416657967</v>
       </c>
-      <c r="BB12">
+      <c r="BF12">
         <v>6.783697783321154</v>
       </c>
-      <c r="BC12">
-        <v>14</v>
-      </c>
-      <c r="BD12">
+      <c r="BG12">
+        <v>14</v>
+      </c>
+      <c r="BH12">
         <v>370316</v>
       </c>
-      <c r="BE12" t="s">
-        <v>46</v>
-      </c>
-      <c r="BF12" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG12" t="s">
-        <v>48</v>
-      </c>
-      <c r="BH12" t="s">
-        <v>54</v>
-      </c>
       <c r="BI12" t="s">
-        <v>60</v>
+        <v>66</v>
+      </c>
+      <c r="BJ12" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK12" t="s">
+        <v>68</v>
+      </c>
+      <c r="BL12" t="s">
+        <v>74</v>
+      </c>
+      <c r="BM12" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:61">
+    <row r="13" spans="1:65">
       <c r="A13" s="1">
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>-0.03417916799729703</v>
@@ -2930,177 +3258,189 @@
         <v>0.9904332417508144</v>
       </c>
       <c r="G13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13">
+        <v>32</v>
+      </c>
+      <c r="H13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13">
         <v>0.000338694688647172</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>0.004741725641060407</v>
       </c>
-      <c r="J13">
-        <v>14</v>
-      </c>
       <c r="K13">
+        <v>14</v>
+      </c>
+      <c r="L13">
         <v>358043</v>
       </c>
-      <c r="L13" t="s">
-        <v>46</v>
-      </c>
       <c r="M13" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="N13" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="O13" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="P13" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="Q13" t="s">
-        <v>20</v>
-      </c>
-      <c r="R13">
+        <v>80</v>
+      </c>
+      <c r="R13" t="s">
+        <v>21</v>
+      </c>
+      <c r="S13">
         <v>-0.03619339271119992</v>
       </c>
-      <c r="S13">
+      <c r="T13">
         <v>0.9644537571194016</v>
       </c>
-      <c r="T13">
+      <c r="U13">
         <v>0.940610276779077</v>
       </c>
-      <c r="U13">
+      <c r="V13">
         <v>0.9889016445864335</v>
       </c>
-      <c r="V13" t="s">
+      <c r="W13" t="s">
+        <v>88</v>
+      </c>
+      <c r="X13" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y13">
+        <v>0.0001959313257346023</v>
+      </c>
+      <c r="Z13">
+        <v>0.002743038560284432</v>
+      </c>
+      <c r="AA13">
+        <v>14</v>
+      </c>
+      <c r="AB13">
+        <v>345147</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE13" t="s">
         <v>68</v>
       </c>
-      <c r="W13">
-        <v>0.0001959313257346023</v>
-      </c>
-      <c r="X13">
-        <v>0.002743038560284432</v>
-      </c>
-      <c r="Y13">
-        <v>14</v>
-      </c>
-      <c r="Z13">
-        <v>345147</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>54</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>60</v>
-      </c>
       <c r="AF13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG13">
+        <v>74</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI13">
         <v>-0.03233453487582353</v>
       </c>
-      <c r="AH13">
+      <c r="AJ13">
         <v>0.9681826370385056</v>
       </c>
-      <c r="AI13">
+      <c r="AK13">
         <v>0.9446856125769243</v>
       </c>
-      <c r="AJ13">
+      <c r="AL13">
         <v>0.9922640994879187</v>
       </c>
-      <c r="AK13" t="s">
-        <v>82</v>
-      </c>
-      <c r="AL13">
+      <c r="AM13" t="s">
+        <v>119</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>133</v>
+      </c>
+      <c r="AO13">
         <v>0.0006988396965541901</v>
       </c>
-      <c r="AM13">
+      <c r="AP13">
         <v>0.009783755751758662</v>
       </c>
-      <c r="AN13">
-        <v>14</v>
-      </c>
-      <c r="AO13">
+      <c r="AQ13">
+        <v>14</v>
+      </c>
+      <c r="AR13">
         <v>358700</v>
       </c>
-      <c r="AP13" t="s">
-        <v>46</v>
-      </c>
-      <c r="AQ13" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR13" t="s">
-        <v>48</v>
-      </c>
       <c r="AS13" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="AT13" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="AU13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV13">
+        <v>68</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>80</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY13">
         <v>-0.03346991171388227</v>
       </c>
-      <c r="AW13">
+      <c r="AZ13">
         <v>0.9670840086940078</v>
       </c>
-      <c r="AX13">
+      <c r="BA13">
         <v>0.9439715879024549</v>
       </c>
-      <c r="AY13">
+      <c r="BB13">
         <v>0.9907623193933627</v>
       </c>
-      <c r="AZ13" t="s">
-        <v>41</v>
-      </c>
-      <c r="BA13">
+      <c r="BC13" t="s">
+        <v>42</v>
+      </c>
+      <c r="BD13" t="s">
+        <v>61</v>
+      </c>
+      <c r="BE13">
         <v>0.0003651241108720283</v>
       </c>
-      <c r="BB13">
+      <c r="BF13">
         <v>0.005111737552208397</v>
       </c>
-      <c r="BC13">
-        <v>14</v>
-      </c>
-      <c r="BD13">
+      <c r="BG13">
+        <v>14</v>
+      </c>
+      <c r="BH13">
         <v>370316</v>
       </c>
-      <c r="BE13" t="s">
-        <v>46</v>
-      </c>
-      <c r="BF13" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG13" t="s">
-        <v>48</v>
-      </c>
-      <c r="BH13" t="s">
-        <v>54</v>
-      </c>
       <c r="BI13" t="s">
-        <v>60</v>
+        <v>66</v>
+      </c>
+      <c r="BJ13" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK13" t="s">
+        <v>68</v>
+      </c>
+      <c r="BL13" t="s">
+        <v>74</v>
+      </c>
+      <c r="BM13" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:61">
+    <row r="14" spans="1:65">
       <c r="A14" s="1">
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>0.8950949442333295</v>
@@ -3115,177 +3455,189 @@
         <v>5.851966132362874</v>
       </c>
       <c r="G14" t="s">
-        <v>32</v>
-      </c>
-      <c r="H14">
+        <v>33</v>
+      </c>
+      <c r="H14" t="s">
+        <v>53</v>
+      </c>
+      <c r="I14">
         <v>0.008168789575711483</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>0.1143630540599608</v>
       </c>
-      <c r="J14">
-        <v>14</v>
-      </c>
       <c r="K14">
+        <v>14</v>
+      </c>
+      <c r="L14">
         <v>370816</v>
       </c>
-      <c r="L14" t="s">
-        <v>42</v>
-      </c>
       <c r="M14" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="N14" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="O14" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="P14" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="Q14" t="s">
-        <v>21</v>
-      </c>
-      <c r="R14">
+        <v>80</v>
+      </c>
+      <c r="R14" t="s">
+        <v>22</v>
+      </c>
+      <c r="S14">
         <v>0.1981452830934524</v>
       </c>
-      <c r="S14">
+      <c r="T14">
         <v>1.21913950131407</v>
       </c>
-      <c r="T14">
+      <c r="U14">
         <v>1.036278940005243</v>
       </c>
-      <c r="U14">
+      <c r="V14">
         <v>1.434267421913253</v>
       </c>
-      <c r="V14" t="s">
+      <c r="W14" t="s">
+        <v>89</v>
+      </c>
+      <c r="X14" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y14">
+        <v>0.001685564984419964</v>
+      </c>
+      <c r="Z14">
+        <v>0.02359790978187949</v>
+      </c>
+      <c r="AA14">
+        <v>14</v>
+      </c>
+      <c r="AB14">
+        <v>362813</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE14" t="s">
         <v>69</v>
       </c>
-      <c r="W14">
-        <v>0.001685564984419964</v>
-      </c>
-      <c r="X14">
-        <v>0.02359790978187949</v>
-      </c>
-      <c r="Y14">
-        <v>14</v>
-      </c>
-      <c r="Z14">
-        <v>362813</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>55</v>
-      </c>
-      <c r="AE14" t="s">
-        <v>60</v>
-      </c>
       <c r="AF14" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG14">
+        <v>75</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI14">
         <v>0.654858437484752</v>
       </c>
-      <c r="AH14">
+      <c r="AJ14">
         <v>1.924870008648358</v>
       </c>
-      <c r="AI14">
+      <c r="AK14">
         <v>0.9480220940850546</v>
       </c>
-      <c r="AJ14">
+      <c r="AL14">
         <v>3.908268144077149</v>
       </c>
-      <c r="AK14" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL14">
+      <c r="AM14" t="s">
+        <v>120</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>134</v>
+      </c>
+      <c r="AO14">
         <v>0.01723305630807608</v>
       </c>
-      <c r="AM14">
+      <c r="AP14">
         <v>0.2412627883130651</v>
       </c>
-      <c r="AN14">
-        <v>14</v>
-      </c>
-      <c r="AO14">
+      <c r="AQ14">
+        <v>14</v>
+      </c>
+      <c r="AR14">
         <v>370314</v>
       </c>
-      <c r="AP14" t="s">
-        <v>42</v>
-      </c>
-      <c r="AQ14" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR14" t="s">
-        <v>49</v>
-      </c>
       <c r="AS14" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="AT14" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="AU14" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV14">
+        <v>69</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AW14" t="s">
+        <v>80</v>
+      </c>
+      <c r="AX14" t="s">
+        <v>22</v>
+      </c>
+      <c r="AY14">
         <v>1.013821663322619</v>
       </c>
-      <c r="AW14">
+      <c r="AZ14">
         <v>2.756113853183478</v>
       </c>
-      <c r="AX14">
+      <c r="BA14">
         <v>1.199866296343989</v>
       </c>
-      <c r="AY14">
+      <c r="BB14">
         <v>6.330841690324585</v>
       </c>
-      <c r="AZ14" t="s">
-        <v>95</v>
-      </c>
-      <c r="BA14">
+      <c r="BC14" t="s">
+        <v>147</v>
+      </c>
+      <c r="BD14" t="s">
+        <v>161</v>
+      </c>
+      <c r="BE14">
         <v>0.001688290541027371</v>
       </c>
-      <c r="BB14">
+      <c r="BF14">
         <v>0.0236360675743832</v>
       </c>
-      <c r="BC14">
-        <v>14</v>
-      </c>
-      <c r="BD14">
+      <c r="BG14">
+        <v>14</v>
+      </c>
+      <c r="BH14">
         <v>373755</v>
       </c>
-      <c r="BE14" t="s">
-        <v>42</v>
-      </c>
-      <c r="BF14" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG14" t="s">
-        <v>49</v>
-      </c>
-      <c r="BH14" t="s">
-        <v>55</v>
-      </c>
       <c r="BI14" t="s">
-        <v>60</v>
+        <v>62</v>
+      </c>
+      <c r="BJ14" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK14" t="s">
+        <v>69</v>
+      </c>
+      <c r="BL14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM14" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:61">
+    <row r="15" spans="1:65">
       <c r="A15" s="1">
         <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15">
         <v>-0.02980799494305779</v>
@@ -3300,177 +3652,189 @@
         <v>0.9896355027357545</v>
       </c>
       <c r="G15" t="s">
-        <v>33</v>
-      </c>
-      <c r="H15">
+        <v>34</v>
+      </c>
+      <c r="H15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I15">
         <v>7.497834810733456E-05</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>0.001049696873502684</v>
       </c>
-      <c r="J15">
-        <v>14</v>
-      </c>
       <c r="K15">
+        <v>14</v>
+      </c>
+      <c r="L15">
         <v>370816</v>
       </c>
-      <c r="L15" t="s">
-        <v>42</v>
-      </c>
       <c r="M15" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="N15" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="O15" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="P15" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="Q15" t="s">
-        <v>20</v>
-      </c>
-      <c r="R15">
+        <v>80</v>
+      </c>
+      <c r="R15" t="s">
+        <v>21</v>
+      </c>
+      <c r="S15">
         <v>-0.03122264803439559</v>
       </c>
-      <c r="S15">
+      <c r="T15">
         <v>0.9692597452729956</v>
       </c>
-      <c r="T15">
+      <c r="U15">
         <v>0.9504511020976617</v>
       </c>
-      <c r="U15">
+      <c r="V15">
         <v>0.9884405959793813</v>
       </c>
-      <c r="V15" t="s">
-        <v>70</v>
-      </c>
-      <c r="W15">
+      <c r="W15" t="s">
+        <v>90</v>
+      </c>
+      <c r="X15" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y15">
         <v>4.058365165931857E-05</v>
       </c>
-      <c r="X15">
+      <c r="Z15">
         <v>0.0005681711232304599</v>
       </c>
-      <c r="Y15">
-        <v>14</v>
-      </c>
-      <c r="Z15">
+      <c r="AA15">
+        <v>14</v>
+      </c>
+      <c r="AB15">
         <v>362813</v>
       </c>
-      <c r="AA15" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>47</v>
-      </c>
       <c r="AC15" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="AD15" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="AE15" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="AF15" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG15">
+        <v>75</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI15">
         <v>-0.02998981705123131</v>
       </c>
-      <c r="AH15">
+      <c r="AJ15">
         <v>0.9704554155959731</v>
       </c>
-      <c r="AI15">
+      <c r="AK15">
         <v>0.9518049136104778</v>
       </c>
-      <c r="AJ15">
+      <c r="AL15">
         <v>0.9894713719086495</v>
       </c>
-      <c r="AK15" t="s">
-        <v>84</v>
-      </c>
-      <c r="AL15">
+      <c r="AM15" t="s">
+        <v>121</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>135</v>
+      </c>
+      <c r="AO15">
         <v>6.8687452567201E-05</v>
       </c>
-      <c r="AM15">
+      <c r="AP15">
         <v>0.000961624335940814</v>
       </c>
-      <c r="AN15">
-        <v>14</v>
-      </c>
-      <c r="AO15">
+      <c r="AQ15">
+        <v>14</v>
+      </c>
+      <c r="AR15">
         <v>370314</v>
       </c>
-      <c r="AP15" t="s">
-        <v>42</v>
-      </c>
-      <c r="AQ15" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR15" t="s">
-        <v>49</v>
-      </c>
       <c r="AS15" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="AT15" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="AU15" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV15">
+        <v>69</v>
+      </c>
+      <c r="AV15" t="s">
+        <v>75</v>
+      </c>
+      <c r="AW15" t="s">
+        <v>80</v>
+      </c>
+      <c r="AX15" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY15">
         <v>-0.02990695457329057</v>
       </c>
-      <c r="AW15">
+      <c r="AZ15">
         <v>0.9705358332681983</v>
       </c>
-      <c r="AX15">
+      <c r="BA15">
         <v>0.9519734650301166</v>
       </c>
-      <c r="AY15">
+      <c r="BB15">
         <v>0.9894601459587918</v>
       </c>
-      <c r="AZ15" t="s">
-        <v>33</v>
-      </c>
-      <c r="BA15">
+      <c r="BC15" t="s">
+        <v>34</v>
+      </c>
+      <c r="BD15" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE15">
         <v>6.630925725338517E-05</v>
       </c>
-      <c r="BB15">
+      <c r="BF15">
         <v>0.0009283296015473924</v>
       </c>
-      <c r="BC15">
-        <v>14</v>
-      </c>
-      <c r="BD15">
+      <c r="BG15">
+        <v>14</v>
+      </c>
+      <c r="BH15">
         <v>373755</v>
       </c>
-      <c r="BE15" t="s">
-        <v>42</v>
-      </c>
-      <c r="BF15" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG15" t="s">
-        <v>49</v>
-      </c>
-      <c r="BH15" t="s">
-        <v>55</v>
-      </c>
       <c r="BI15" t="s">
-        <v>60</v>
+        <v>62</v>
+      </c>
+      <c r="BJ15" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK15" t="s">
+        <v>69</v>
+      </c>
+      <c r="BL15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM15" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:61">
+    <row r="16" spans="1:65">
       <c r="A16" s="1">
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16">
         <v>-3.145700962614749</v>
@@ -3485,177 +3849,189 @@
         <v>0.2595646983974518</v>
       </c>
       <c r="G16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16">
+        <v>35</v>
+      </c>
+      <c r="H16" t="s">
+        <v>55</v>
+      </c>
+      <c r="I16">
         <v>6.507694044682279E-06</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>9.110771662555192E-05</v>
       </c>
-      <c r="J16">
-        <v>14</v>
-      </c>
       <c r="K16">
+        <v>14</v>
+      </c>
+      <c r="L16">
         <v>369117</v>
       </c>
-      <c r="L16" t="s">
-        <v>43</v>
-      </c>
       <c r="M16" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="N16" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="O16" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="P16" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="Q16" t="s">
-        <v>21</v>
-      </c>
-      <c r="R16">
+        <v>81</v>
+      </c>
+      <c r="R16" t="s">
+        <v>22</v>
+      </c>
+      <c r="S16">
         <v>-0.5123703039464149</v>
       </c>
-      <c r="S16">
+      <c r="T16">
         <v>0.5990739073343793</v>
       </c>
-      <c r="T16">
+      <c r="U16">
         <v>0.4290163113821664</v>
       </c>
-      <c r="U16">
+      <c r="V16">
         <v>0.8365405625083163</v>
       </c>
-      <c r="V16" t="s">
-        <v>71</v>
-      </c>
-      <c r="W16">
+      <c r="W16" t="s">
+        <v>91</v>
+      </c>
+      <c r="X16" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y16">
         <v>7.72633597806051E-05</v>
       </c>
-      <c r="X16">
+      <c r="Z16">
         <v>0.001081687036928471</v>
       </c>
-      <c r="Y16">
-        <v>14</v>
-      </c>
-      <c r="Z16">
+      <c r="AA16">
+        <v>14</v>
+      </c>
+      <c r="AB16">
         <v>361143</v>
       </c>
-      <c r="AA16" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>47</v>
-      </c>
       <c r="AC16" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="AD16" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="AE16" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="AF16" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG16">
+        <v>76</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI16">
         <v>-2.502223866607008</v>
       </c>
-      <c r="AH16">
+      <c r="AJ16">
         <v>0.08190265536521425</v>
       </c>
-      <c r="AI16">
+      <c r="AK16">
         <v>0.01926338973653045</v>
       </c>
-      <c r="AJ16">
+      <c r="AL16">
         <v>0.348227650876634</v>
       </c>
-      <c r="AK16" t="s">
-        <v>85</v>
-      </c>
-      <c r="AL16">
+      <c r="AM16" t="s">
+        <v>122</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>136</v>
+      </c>
+      <c r="AO16">
         <v>8.457979468637617E-06</v>
       </c>
-      <c r="AM16">
+      <c r="AP16">
         <v>0.0001184117125609266</v>
       </c>
-      <c r="AN16">
-        <v>14</v>
-      </c>
-      <c r="AO16">
+      <c r="AQ16">
+        <v>14</v>
+      </c>
+      <c r="AR16">
         <v>368616</v>
       </c>
-      <c r="AP16" t="s">
-        <v>43</v>
-      </c>
-      <c r="AQ16" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR16" t="s">
-        <v>49</v>
-      </c>
       <c r="AS16" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="AT16" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="AU16" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV16">
+        <v>69</v>
+      </c>
+      <c r="AV16" t="s">
+        <v>76</v>
+      </c>
+      <c r="AW16" t="s">
+        <v>81</v>
+      </c>
+      <c r="AX16" t="s">
+        <v>22</v>
+      </c>
+      <c r="AY16">
         <v>-3.931057888896422</v>
       </c>
-      <c r="AW16">
+      <c r="AZ16">
         <v>0.0196229027180124</v>
       </c>
-      <c r="AX16">
+      <c r="BA16">
         <v>0.003624728219533491</v>
       </c>
-      <c r="AY16">
+      <c r="BB16">
         <v>0.1062309469177626</v>
       </c>
-      <c r="AZ16" t="s">
-        <v>96</v>
-      </c>
-      <c r="BA16">
+      <c r="BC16" t="s">
+        <v>148</v>
+      </c>
+      <c r="BD16" t="s">
+        <v>162</v>
+      </c>
+      <c r="BE16">
         <v>2.029891275315582E-09</v>
       </c>
-      <c r="BB16">
+      <c r="BF16">
         <v>2.841847785441815E-08</v>
       </c>
-      <c r="BC16">
-        <v>14</v>
-      </c>
-      <c r="BD16">
+      <c r="BG16">
+        <v>14</v>
+      </c>
+      <c r="BH16">
         <v>372032</v>
       </c>
-      <c r="BE16" t="s">
-        <v>43</v>
-      </c>
-      <c r="BF16" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG16" t="s">
-        <v>49</v>
-      </c>
-      <c r="BH16" t="s">
-        <v>56</v>
-      </c>
       <c r="BI16" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="BJ16" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK16" t="s">
+        <v>69</v>
+      </c>
+      <c r="BL16" t="s">
+        <v>76</v>
+      </c>
+      <c r="BM16" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:61">
+    <row r="17" spans="1:65">
       <c r="A17" s="1">
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17">
         <v>0.3639558526803731</v>
@@ -3670,177 +4046,189 @@
         <v>1.495403034287387</v>
       </c>
       <c r="G17" t="s">
-        <v>35</v>
-      </c>
-      <c r="H17">
+        <v>36</v>
+      </c>
+      <c r="H17" t="s">
+        <v>56</v>
+      </c>
+      <c r="I17">
         <v>2.270104497060272E-131</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>3.178146295884381E-130</v>
       </c>
-      <c r="J17">
-        <v>14</v>
-      </c>
       <c r="K17">
+        <v>14</v>
+      </c>
+      <c r="L17">
         <v>369117</v>
       </c>
-      <c r="L17" t="s">
-        <v>43</v>
-      </c>
       <c r="M17" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="N17" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="O17" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="P17" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="Q17" t="s">
-        <v>20</v>
-      </c>
-      <c r="R17">
+        <v>81</v>
+      </c>
+      <c r="R17" t="s">
+        <v>21</v>
+      </c>
+      <c r="S17">
         <v>0.3650148159953517</v>
       </c>
-      <c r="S17">
+      <c r="T17">
         <v>1.440535350956173</v>
       </c>
-      <c r="T17">
+      <c r="U17">
         <v>1.385615680387573</v>
       </c>
-      <c r="U17">
+      <c r="V17">
         <v>1.497631794101798</v>
       </c>
-      <c r="V17" t="s">
-        <v>72</v>
-      </c>
-      <c r="W17">
+      <c r="W17" t="s">
+        <v>92</v>
+      </c>
+      <c r="X17" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y17">
         <v>2.93422051176933E-129</v>
       </c>
-      <c r="X17">
+      <c r="Z17">
         <v>4.107908716477062E-128</v>
       </c>
-      <c r="Y17">
-        <v>14</v>
-      </c>
-      <c r="Z17">
+      <c r="AA17">
+        <v>14</v>
+      </c>
+      <c r="AB17">
         <v>361143</v>
       </c>
-      <c r="AA17" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB17" t="s">
-        <v>47</v>
-      </c>
       <c r="AC17" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="AD17" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="AE17" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="AF17" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG17">
+        <v>76</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI17">
         <v>0.3640339228624073</v>
       </c>
-      <c r="AH17">
+      <c r="AJ17">
         <v>1.439123032502631</v>
       </c>
-      <c r="AI17">
+      <c r="AK17">
         <v>1.384812003297968</v>
       </c>
-      <c r="AJ17">
+      <c r="AL17">
         <v>1.49556408938343</v>
       </c>
-      <c r="AK17" t="s">
-        <v>35</v>
-      </c>
-      <c r="AL17">
+      <c r="AM17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>137</v>
+      </c>
+      <c r="AO17">
         <v>3.160822404906091E-131</v>
       </c>
-      <c r="AM17">
+      <c r="AP17">
         <v>4.425151366868527E-130</v>
       </c>
-      <c r="AN17">
-        <v>14</v>
-      </c>
-      <c r="AO17">
+      <c r="AQ17">
+        <v>14</v>
+      </c>
+      <c r="AR17">
         <v>368616</v>
       </c>
-      <c r="AP17" t="s">
-        <v>43</v>
-      </c>
-      <c r="AQ17" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR17" t="s">
-        <v>49</v>
-      </c>
       <c r="AS17" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="AT17" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="AU17" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV17">
+        <v>69</v>
+      </c>
+      <c r="AV17" t="s">
+        <v>76</v>
+      </c>
+      <c r="AW17" t="s">
+        <v>81</v>
+      </c>
+      <c r="AX17" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY17">
         <v>0.3628122571491498</v>
       </c>
-      <c r="AW17">
+      <c r="AZ17">
         <v>1.437365978721373</v>
       </c>
-      <c r="AX17">
+      <c r="BA17">
         <v>1.383366114906155</v>
       </c>
-      <c r="AY17">
+      <c r="BB17">
         <v>1.493473733759775</v>
       </c>
-      <c r="AZ17" t="s">
-        <v>91</v>
-      </c>
-      <c r="BA17">
+      <c r="BC17" t="s">
+        <v>143</v>
+      </c>
+      <c r="BD17" t="s">
+        <v>163</v>
+      </c>
+      <c r="BE17">
         <v>1.500323928434213E-131</v>
       </c>
-      <c r="BB17">
+      <c r="BF17">
         <v>2.100453499807897E-130</v>
       </c>
-      <c r="BC17">
-        <v>14</v>
-      </c>
-      <c r="BD17">
+      <c r="BG17">
+        <v>14</v>
+      </c>
+      <c r="BH17">
         <v>372032</v>
       </c>
-      <c r="BE17" t="s">
-        <v>43</v>
-      </c>
-      <c r="BF17" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG17" t="s">
-        <v>49</v>
-      </c>
-      <c r="BH17" t="s">
-        <v>56</v>
-      </c>
       <c r="BI17" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="BJ17" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK17" t="s">
+        <v>69</v>
+      </c>
+      <c r="BL17" t="s">
+        <v>76</v>
+      </c>
+      <c r="BM17" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:61">
+    <row r="18" spans="1:65">
       <c r="A18" s="1">
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18">
         <v>0.2878587353780683</v>
@@ -3855,177 +4243,189 @@
         <v>1.904359305563377</v>
       </c>
       <c r="G18" t="s">
-        <v>36</v>
-      </c>
-      <c r="H18">
+        <v>37</v>
+      </c>
+      <c r="H18" t="s">
+        <v>57</v>
+      </c>
+      <c r="I18">
         <v>0.03742313301336047</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>0.5239238621870466</v>
       </c>
-      <c r="J18">
-        <v>14</v>
-      </c>
       <c r="K18">
+        <v>14</v>
+      </c>
+      <c r="L18">
         <v>372590</v>
       </c>
-      <c r="L18" t="s">
-        <v>44</v>
-      </c>
       <c r="M18" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="N18" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="O18" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="P18" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="Q18" t="s">
-        <v>21</v>
-      </c>
-      <c r="R18">
+        <v>81</v>
+      </c>
+      <c r="R18" t="s">
+        <v>22</v>
+      </c>
+      <c r="S18">
         <v>0.1083781323516554</v>
       </c>
-      <c r="S18">
+      <c r="T18">
         <v>1.11446908253587</v>
       </c>
-      <c r="T18">
+      <c r="U18">
         <v>1.042991050443133</v>
       </c>
-      <c r="U18">
+      <c r="V18">
         <v>1.190845631322188</v>
       </c>
-      <c r="V18" t="s">
-        <v>73</v>
-      </c>
-      <c r="W18">
+      <c r="W18" t="s">
+        <v>93</v>
+      </c>
+      <c r="X18" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y18">
         <v>2.536461537400428E-05</v>
       </c>
-      <c r="X18">
+      <c r="Z18">
         <v>0.00035510461523606</v>
       </c>
-      <c r="Y18">
-        <v>14</v>
-      </c>
-      <c r="Z18">
+      <c r="AA18">
+        <v>14</v>
+      </c>
+      <c r="AB18">
         <v>364553</v>
       </c>
-      <c r="AA18" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB18" t="s">
-        <v>47</v>
-      </c>
       <c r="AC18" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="AD18" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="AE18" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="AF18" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG18">
+        <v>77</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI18">
         <v>0.1330353170285861</v>
       </c>
-      <c r="AH18">
+      <c r="AJ18">
         <v>1.142290339919106</v>
       </c>
-      <c r="AI18">
+      <c r="AK18">
         <v>0.8573178327084943</v>
       </c>
-      <c r="AJ18">
+      <c r="AL18">
         <v>1.521987728343655</v>
       </c>
-      <c r="AK18" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL18">
+      <c r="AM18" t="s">
+        <v>123</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO18">
         <v>0.2324508391775847</v>
       </c>
-      <c r="AM18">
+      <c r="AP18">
         <v>3.254311748486185</v>
       </c>
-      <c r="AN18">
-        <v>14</v>
-      </c>
-      <c r="AO18">
+      <c r="AQ18">
+        <v>14</v>
+      </c>
+      <c r="AR18">
         <v>372086</v>
       </c>
-      <c r="AP18" t="s">
-        <v>44</v>
-      </c>
-      <c r="AQ18" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR18" t="s">
-        <v>49</v>
-      </c>
       <c r="AS18" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="AT18" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="AU18" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV18">
+        <v>69</v>
+      </c>
+      <c r="AV18" t="s">
+        <v>77</v>
+      </c>
+      <c r="AW18" t="s">
+        <v>81</v>
+      </c>
+      <c r="AX18" t="s">
+        <v>22</v>
+      </c>
+      <c r="AY18">
         <v>0.5464010850006225</v>
       </c>
-      <c r="AW18">
+      <c r="AZ18">
         <v>1.727026398840675</v>
       </c>
-      <c r="AX18">
+      <c r="BA18">
         <v>1.234984055032314</v>
       </c>
-      <c r="AY18">
+      <c r="BB18">
         <v>2.415108251915487</v>
       </c>
-      <c r="AZ18" t="s">
-        <v>97</v>
-      </c>
-      <c r="BA18">
+      <c r="BC18" t="s">
+        <v>149</v>
+      </c>
+      <c r="BD18" t="s">
+        <v>164</v>
+      </c>
+      <c r="BE18">
         <v>2.704694959580835E-05</v>
       </c>
-      <c r="BB18">
+      <c r="BF18">
         <v>0.0003786572943413169</v>
       </c>
-      <c r="BC18">
-        <v>14</v>
-      </c>
-      <c r="BD18">
+      <c r="BG18">
+        <v>14</v>
+      </c>
+      <c r="BH18">
         <v>375544</v>
       </c>
-      <c r="BE18" t="s">
-        <v>44</v>
-      </c>
-      <c r="BF18" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG18" t="s">
-        <v>49</v>
-      </c>
-      <c r="BH18" t="s">
-        <v>57</v>
-      </c>
       <c r="BI18" t="s">
-        <v>61</v>
+        <v>64</v>
+      </c>
+      <c r="BJ18" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK18" t="s">
+        <v>69</v>
+      </c>
+      <c r="BL18" t="s">
+        <v>77</v>
+      </c>
+      <c r="BM18" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:61">
+    <row r="19" spans="1:65">
       <c r="A19" s="1">
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>-0.1276620692388169</v>
@@ -4040,177 +4440,189 @@
         <v>0.88689221142915</v>
       </c>
       <c r="G19" t="s">
-        <v>37</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="H19" t="s">
+        <v>48</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K19">
+        <v>14</v>
+      </c>
+      <c r="L19">
         <v>372590</v>
       </c>
-      <c r="L19" t="s">
-        <v>44</v>
-      </c>
       <c r="M19" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="N19" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="O19" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="P19" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="Q19" t="s">
-        <v>20</v>
-      </c>
-      <c r="R19">
+        <v>81</v>
+      </c>
+      <c r="R19" t="s">
+        <v>21</v>
+      </c>
+      <c r="S19">
         <v>-0.1274816226192603</v>
       </c>
-      <c r="S19">
+      <c r="T19">
         <v>0.8803095934701374</v>
       </c>
-      <c r="T19">
+      <c r="U19">
         <v>0.8735442632035514</v>
       </c>
-      <c r="U19">
+      <c r="V19">
         <v>0.8871273191281694</v>
       </c>
-      <c r="V19" t="s">
-        <v>27</v>
-      </c>
-      <c r="W19">
+      <c r="W19" t="s">
+        <v>28</v>
+      </c>
+      <c r="X19" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y19">
         <v>0</v>
       </c>
-      <c r="X19">
+      <c r="Z19">
         <v>0</v>
       </c>
-      <c r="Y19">
-        <v>14</v>
-      </c>
-      <c r="Z19">
+      <c r="AA19">
+        <v>14</v>
+      </c>
+      <c r="AB19">
         <v>364553</v>
       </c>
-      <c r="AA19" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB19" t="s">
-        <v>47</v>
-      </c>
       <c r="AC19" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="AD19" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="AE19" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="AF19" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG19">
+        <v>77</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI19">
         <v>-0.1275498448187025</v>
       </c>
-      <c r="AH19">
+      <c r="AJ19">
         <v>0.8802495388620328</v>
       </c>
-      <c r="AI19">
+      <c r="AK19">
         <v>0.8735530304376111</v>
       </c>
-      <c r="AJ19">
+      <c r="AL19">
         <v>0.886997381577008</v>
       </c>
-      <c r="AK19" t="s">
-        <v>37</v>
-      </c>
-      <c r="AL19">
+      <c r="AM19" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO19">
         <v>0</v>
       </c>
-      <c r="AM19">
+      <c r="AP19">
         <v>0</v>
       </c>
-      <c r="AN19">
-        <v>14</v>
-      </c>
-      <c r="AO19">
+      <c r="AQ19">
+        <v>14</v>
+      </c>
+      <c r="AR19">
         <v>372086</v>
       </c>
-      <c r="AP19" t="s">
-        <v>44</v>
-      </c>
-      <c r="AQ19" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR19" t="s">
-        <v>49</v>
-      </c>
       <c r="AS19" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="AT19" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="AU19" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV19">
+        <v>69</v>
+      </c>
+      <c r="AV19" t="s">
+        <v>77</v>
+      </c>
+      <c r="AW19" t="s">
+        <v>81</v>
+      </c>
+      <c r="AX19" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY19">
         <v>-0.1276978281290604</v>
       </c>
-      <c r="AW19">
+      <c r="AZ19">
         <v>0.8801192862591743</v>
       </c>
-      <c r="AX19">
+      <c r="BA19">
         <v>0.8734554516695103</v>
       </c>
-      <c r="AY19">
+      <c r="BB19">
         <v>0.8868339610964474</v>
       </c>
-      <c r="AZ19" t="s">
-        <v>37</v>
-      </c>
-      <c r="BA19">
+      <c r="BC19" t="s">
+        <v>38</v>
+      </c>
+      <c r="BD19" t="s">
+        <v>48</v>
+      </c>
+      <c r="BE19">
         <v>0</v>
       </c>
-      <c r="BB19">
+      <c r="BF19">
         <v>0</v>
       </c>
-      <c r="BC19">
-        <v>14</v>
-      </c>
-      <c r="BD19">
+      <c r="BG19">
+        <v>14</v>
+      </c>
+      <c r="BH19">
         <v>375544</v>
       </c>
-      <c r="BE19" t="s">
-        <v>44</v>
-      </c>
-      <c r="BF19" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG19" t="s">
-        <v>49</v>
-      </c>
-      <c r="BH19" t="s">
-        <v>57</v>
-      </c>
       <c r="BI19" t="s">
-        <v>61</v>
+        <v>64</v>
+      </c>
+      <c r="BJ19" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK19" t="s">
+        <v>69</v>
+      </c>
+      <c r="BL19" t="s">
+        <v>77</v>
+      </c>
+      <c r="BM19" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="20" spans="1:61">
+    <row r="20" spans="1:65">
       <c r="A20" s="1">
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>-1.014047541548214</v>
@@ -4225,177 +4637,189 @@
         <v>1.404505225133976</v>
       </c>
       <c r="G20" t="s">
-        <v>38</v>
-      </c>
-      <c r="H20">
+        <v>39</v>
+      </c>
+      <c r="H20" t="s">
+        <v>58</v>
+      </c>
+      <c r="I20">
         <v>0.05367007850767107</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>0.7513810991073949</v>
       </c>
-      <c r="J20">
-        <v>14</v>
-      </c>
       <c r="K20">
+        <v>14</v>
+      </c>
+      <c r="L20">
         <v>119436</v>
       </c>
-      <c r="L20" t="s">
-        <v>45</v>
-      </c>
       <c r="M20" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="N20" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="O20" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="P20" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="Q20" t="s">
-        <v>21</v>
-      </c>
-      <c r="R20">
+        <v>81</v>
+      </c>
+      <c r="R20" t="s">
+        <v>22</v>
+      </c>
+      <c r="S20">
         <v>-0.249073671282315</v>
       </c>
-      <c r="S20">
+      <c r="T20">
         <v>0.7795225428439108</v>
       </c>
-      <c r="T20">
+      <c r="U20">
         <v>0.6006578855856683</v>
       </c>
-      <c r="U20">
+      <c r="V20">
         <v>1.01164974169838</v>
       </c>
-      <c r="V20" t="s">
-        <v>74</v>
-      </c>
-      <c r="W20">
+      <c r="W20" t="s">
+        <v>94</v>
+      </c>
+      <c r="X20" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y20">
         <v>0.0138407232126579</v>
       </c>
-      <c r="X20">
+      <c r="Z20">
         <v>0.1937701249772106</v>
       </c>
-      <c r="Y20">
-        <v>14</v>
-      </c>
-      <c r="Z20">
+      <c r="AA20">
+        <v>14</v>
+      </c>
+      <c r="AB20">
         <v>116841</v>
       </c>
-      <c r="AA20" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>47</v>
-      </c>
       <c r="AC20" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="AD20" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="AE20" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="AF20" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG20">
+        <v>78</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI20">
         <v>-0.6631282098968091</v>
       </c>
-      <c r="AH20">
+      <c r="AJ20">
         <v>0.515237041272391</v>
       </c>
-      <c r="AI20">
+      <c r="AK20">
         <v>0.1704345930372407</v>
       </c>
-      <c r="AJ20">
+      <c r="AL20">
         <v>1.557601681491512</v>
       </c>
-      <c r="AK20" t="s">
-        <v>87</v>
-      </c>
-      <c r="AL20">
+      <c r="AM20" t="s">
+        <v>124</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>139</v>
+      </c>
+      <c r="AO20">
         <v>0.1225848819466495</v>
       </c>
-      <c r="AM20">
+      <c r="AP20">
         <v>1.716188347253093</v>
       </c>
-      <c r="AN20">
-        <v>14</v>
-      </c>
-      <c r="AO20">
+      <c r="AQ20">
+        <v>14</v>
+      </c>
+      <c r="AR20">
         <v>119282</v>
       </c>
-      <c r="AP20" t="s">
-        <v>45</v>
-      </c>
-      <c r="AQ20" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR20" t="s">
-        <v>49</v>
-      </c>
       <c r="AS20" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="AT20" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="AU20" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV20">
+        <v>69</v>
+      </c>
+      <c r="AV20" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW20" t="s">
+        <v>81</v>
+      </c>
+      <c r="AX20" t="s">
+        <v>22</v>
+      </c>
+      <c r="AY20">
         <v>-1.419757542408124</v>
       </c>
-      <c r="AW20">
+      <c r="AZ20">
         <v>0.2417726294007322</v>
       </c>
-      <c r="AX20">
+      <c r="BA20">
         <v>0.0647672420151654</v>
       </c>
-      <c r="AY20">
+      <c r="BB20">
         <v>0.9025242160791197</v>
       </c>
-      <c r="AZ20" t="s">
-        <v>98</v>
-      </c>
-      <c r="BA20">
+      <c r="BC20" t="s">
+        <v>150</v>
+      </c>
+      <c r="BD20" t="s">
+        <v>165</v>
+      </c>
+      <c r="BE20">
         <v>0.005496644652762488</v>
       </c>
-      <c r="BB20">
+      <c r="BF20">
         <v>0.07695302513867483</v>
       </c>
-      <c r="BC20">
-        <v>14</v>
-      </c>
-      <c r="BD20">
+      <c r="BG20">
+        <v>14</v>
+      </c>
+      <c r="BH20">
         <v>120400</v>
       </c>
-      <c r="BE20" t="s">
-        <v>45</v>
-      </c>
-      <c r="BF20" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG20" t="s">
-        <v>49</v>
-      </c>
-      <c r="BH20" t="s">
-        <v>58</v>
-      </c>
       <c r="BI20" t="s">
-        <v>61</v>
+        <v>65</v>
+      </c>
+      <c r="BJ20" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK20" t="s">
+        <v>69</v>
+      </c>
+      <c r="BL20" t="s">
+        <v>78</v>
+      </c>
+      <c r="BM20" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:61">
+    <row r="21" spans="1:65">
       <c r="A21" s="1">
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C21">
         <v>0.2433719516318178</v>
@@ -4410,177 +4834,189 @@
         <v>1.312188563830422</v>
       </c>
       <c r="G21" t="s">
-        <v>39</v>
-      </c>
-      <c r="H21">
+        <v>40</v>
+      </c>
+      <c r="H21" t="s">
+        <v>59</v>
+      </c>
+      <c r="I21">
         <v>1.545705624628348E-108</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>2.163987874479687E-107</v>
       </c>
-      <c r="J21">
-        <v>14</v>
-      </c>
       <c r="K21">
+        <v>14</v>
+      </c>
+      <c r="L21">
         <v>119436</v>
       </c>
-      <c r="L21" t="s">
-        <v>45</v>
-      </c>
       <c r="M21" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="N21" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="O21" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="P21" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="Q21" t="s">
-        <v>20</v>
-      </c>
-      <c r="R21">
+        <v>81</v>
+      </c>
+      <c r="R21" t="s">
+        <v>21</v>
+      </c>
+      <c r="S21">
         <v>0.2445721710287801</v>
       </c>
-      <c r="S21">
+      <c r="T21">
         <v>1.277074826702564</v>
       </c>
-      <c r="T21">
+      <c r="U21">
         <v>1.240990888029757</v>
       </c>
-      <c r="U21">
+      <c r="V21">
         <v>1.314207967785077</v>
       </c>
-      <c r="V21" t="s">
-        <v>75</v>
-      </c>
-      <c r="W21">
+      <c r="W21" t="s">
+        <v>95</v>
+      </c>
+      <c r="X21" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y21">
         <v>4.525643008612384E-107</v>
       </c>
-      <c r="X21">
+      <c r="Z21">
         <v>6.335900212057337E-106</v>
       </c>
-      <c r="Y21">
-        <v>14</v>
-      </c>
-      <c r="Z21">
+      <c r="AA21">
+        <v>14</v>
+      </c>
+      <c r="AB21">
         <v>116841</v>
       </c>
-      <c r="AA21" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB21" t="s">
-        <v>47</v>
-      </c>
       <c r="AC21" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="AD21" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="AE21" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="AF21" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG21">
+        <v>78</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI21">
         <v>0.2433738037879405</v>
       </c>
-      <c r="AH21">
+      <c r="AJ21">
         <v>1.275545338693345</v>
       </c>
-      <c r="AI21">
+      <c r="AK21">
         <v>1.239897304796695</v>
       </c>
-      <c r="AJ21">
+      <c r="AL21">
         <v>1.312218281923841</v>
       </c>
-      <c r="AK21" t="s">
-        <v>39</v>
-      </c>
-      <c r="AL21">
+      <c r="AM21" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO21">
         <v>2.207180966726187E-108</v>
       </c>
-      <c r="AM21">
+      <c r="AP21">
         <v>3.090053353416661E-107</v>
       </c>
-      <c r="AN21">
-        <v>14</v>
-      </c>
-      <c r="AO21">
+      <c r="AQ21">
+        <v>14</v>
+      </c>
+      <c r="AR21">
         <v>119282</v>
       </c>
-      <c r="AP21" t="s">
-        <v>45</v>
-      </c>
-      <c r="AQ21" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR21" t="s">
-        <v>49</v>
-      </c>
       <c r="AS21" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="AT21" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="AU21" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV21">
+        <v>69</v>
+      </c>
+      <c r="AV21" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW21" t="s">
+        <v>81</v>
+      </c>
+      <c r="AX21" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY21">
         <v>0.2438137653345538</v>
       </c>
-      <c r="AW21">
+      <c r="AZ21">
         <v>1.276106653062647</v>
       </c>
-      <c r="AX21">
+      <c r="BA21">
         <v>1.240600101248857</v>
       </c>
-      <c r="AY21">
+      <c r="BB21">
         <v>1.312629418900953</v>
       </c>
-      <c r="AZ21" t="s">
-        <v>99</v>
-      </c>
-      <c r="BA21">
+      <c r="BC21" t="s">
+        <v>151</v>
+      </c>
+      <c r="BD21" t="s">
+        <v>166</v>
+      </c>
+      <c r="BE21">
         <v>9.940505717337853E-110</v>
       </c>
-      <c r="BB21">
+      <c r="BF21">
         <v>1.391670800427299E-108</v>
       </c>
-      <c r="BC21">
-        <v>14</v>
-      </c>
-      <c r="BD21">
+      <c r="BG21">
+        <v>14</v>
+      </c>
+      <c r="BH21">
         <v>120400</v>
       </c>
-      <c r="BE21" t="s">
-        <v>45</v>
-      </c>
-      <c r="BF21" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG21" t="s">
-        <v>49</v>
-      </c>
-      <c r="BH21" t="s">
-        <v>58</v>
-      </c>
       <c r="BI21" t="s">
-        <v>61</v>
+        <v>65</v>
+      </c>
+      <c r="BJ21" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK21" t="s">
+        <v>69</v>
+      </c>
+      <c r="BL21" t="s">
+        <v>78</v>
+      </c>
+      <c r="BM21" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:61">
+    <row r="22" spans="1:65">
       <c r="A22" s="1">
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C22">
         <v>-0.1933385967266682</v>
@@ -4595,177 +5031,189 @@
         <v>2.607114571439411</v>
       </c>
       <c r="G22" t="s">
-        <v>40</v>
-      </c>
-      <c r="H22">
+        <v>41</v>
+      </c>
+      <c r="H22" t="s">
+        <v>60</v>
+      </c>
+      <c r="I22">
         <v>0.6654110443964876</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>9.315754621550827</v>
       </c>
-      <c r="J22">
-        <v>14</v>
-      </c>
       <c r="K22">
+        <v>14</v>
+      </c>
+      <c r="L22">
         <v>371864</v>
       </c>
-      <c r="L22" t="s">
-        <v>46</v>
-      </c>
       <c r="M22" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="N22" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="O22" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="P22" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="Q22" t="s">
-        <v>21</v>
-      </c>
-      <c r="R22">
+        <v>80</v>
+      </c>
+      <c r="R22" t="s">
+        <v>22</v>
+      </c>
+      <c r="S22">
         <v>0.05802381637808663</v>
       </c>
-      <c r="S22">
+      <c r="T22">
         <v>1.059740234583838</v>
       </c>
-      <c r="T22">
+      <c r="U22">
         <v>0.8620170278282873</v>
       </c>
-      <c r="U22">
+      <c r="V22">
         <v>1.302815754840886</v>
       </c>
-      <c r="V22" t="s">
-        <v>76</v>
-      </c>
-      <c r="W22">
+      <c r="W22" t="s">
+        <v>96</v>
+      </c>
+      <c r="X22" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y22">
         <v>0.4692129116876891</v>
       </c>
-      <c r="X22">
+      <c r="Z22">
         <v>6.568980763627647</v>
       </c>
-      <c r="Y22">
-        <v>14</v>
-      </c>
-      <c r="Z22">
+      <c r="AA22">
+        <v>14</v>
+      </c>
+      <c r="AB22">
         <v>363838</v>
       </c>
-      <c r="AA22" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB22" t="s">
-        <v>47</v>
-      </c>
       <c r="AC22" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="AD22" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="AE22" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="AF22" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG22">
+        <v>79</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI22">
         <v>0.008689225058483312</v>
       </c>
-      <c r="AH22">
+      <c r="AJ22">
         <v>1.008727085955709</v>
       </c>
-      <c r="AI22">
+      <c r="AK22">
         <v>0.4057936947425411</v>
       </c>
-      <c r="AJ22">
+      <c r="AL22">
         <v>2.507506516547224</v>
       </c>
-      <c r="AK22" t="s">
-        <v>88</v>
-      </c>
-      <c r="AL22">
+      <c r="AM22" t="s">
+        <v>125</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>140</v>
+      </c>
+      <c r="AO22">
         <v>0.9803904784664456</v>
       </c>
-      <c r="AM22">
+      <c r="AP22">
         <v>13.72546669853024</v>
       </c>
-      <c r="AN22">
-        <v>14</v>
-      </c>
-      <c r="AO22">
+      <c r="AQ22">
+        <v>14</v>
+      </c>
+      <c r="AR22">
         <v>371359</v>
       </c>
-      <c r="AP22" t="s">
-        <v>46</v>
-      </c>
-      <c r="AQ22" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR22" t="s">
-        <v>49</v>
-      </c>
       <c r="AS22" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="AT22" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="AU22" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV22">
+        <v>69</v>
+      </c>
+      <c r="AV22" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW22" t="s">
+        <v>80</v>
+      </c>
+      <c r="AX22" t="s">
+        <v>22</v>
+      </c>
+      <c r="AY22">
         <v>0.380260717589908</v>
       </c>
-      <c r="AW22">
+      <c r="AZ22">
         <v>1.46266588245088</v>
       </c>
-      <c r="AX22">
+      <c r="BA22">
         <v>0.5122659239300569</v>
       </c>
-      <c r="AY22">
+      <c r="BB22">
         <v>4.176329878186308</v>
       </c>
-      <c r="AZ22" t="s">
-        <v>100</v>
-      </c>
-      <c r="BA22">
+      <c r="BC22" t="s">
+        <v>152</v>
+      </c>
+      <c r="BD22" t="s">
+        <v>167</v>
+      </c>
+      <c r="BE22">
         <v>0.3505202966972515</v>
       </c>
-      <c r="BB22">
+      <c r="BF22">
         <v>4.907284153761521</v>
       </c>
-      <c r="BC22">
-        <v>14</v>
-      </c>
-      <c r="BD22">
+      <c r="BG22">
+        <v>14</v>
+      </c>
+      <c r="BH22">
         <v>374808</v>
       </c>
-      <c r="BE22" t="s">
-        <v>46</v>
-      </c>
-      <c r="BF22" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG22" t="s">
-        <v>49</v>
-      </c>
-      <c r="BH22" t="s">
-        <v>59</v>
-      </c>
       <c r="BI22" t="s">
-        <v>60</v>
+        <v>66</v>
+      </c>
+      <c r="BJ22" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK22" t="s">
+        <v>69</v>
+      </c>
+      <c r="BL22" t="s">
+        <v>79</v>
+      </c>
+      <c r="BM22" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="23" spans="1:61">
+    <row r="23" spans="1:65">
       <c r="A23" s="1">
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C23">
         <v>-0.03343098367934854</v>
@@ -4780,177 +5228,189 @@
         <v>0.9907431073634442</v>
       </c>
       <c r="G23" t="s">
-        <v>41</v>
-      </c>
-      <c r="H23">
+        <v>42</v>
+      </c>
+      <c r="H23" t="s">
+        <v>61</v>
+      </c>
+      <c r="I23">
         <v>0.0003589680552533581</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>0.005025552773547014</v>
       </c>
-      <c r="J23">
-        <v>14</v>
-      </c>
       <c r="K23">
+        <v>14</v>
+      </c>
+      <c r="L23">
         <v>371864</v>
       </c>
-      <c r="L23" t="s">
-        <v>46</v>
-      </c>
       <c r="M23" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="N23" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="O23" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="P23" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="Q23" t="s">
-        <v>20</v>
-      </c>
-      <c r="R23">
+        <v>80</v>
+      </c>
+      <c r="R23" t="s">
+        <v>21</v>
+      </c>
+      <c r="S23">
         <v>-0.03426308096931899</v>
       </c>
-      <c r="S23">
+      <c r="T23">
         <v>0.9663172515151959</v>
       </c>
-      <c r="T23">
+      <c r="U23">
         <v>0.9430358779192286</v>
       </c>
-      <c r="U23">
+      <c r="V23">
         <v>0.9901733883510422</v>
       </c>
-      <c r="V23" t="s">
-        <v>31</v>
-      </c>
-      <c r="W23">
+      <c r="W23" t="s">
+        <v>32</v>
+      </c>
+      <c r="X23" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y23">
         <v>0.0002959241669304901</v>
       </c>
-      <c r="X23">
+      <c r="Z23">
         <v>0.004142938337026862</v>
       </c>
-      <c r="Y23">
-        <v>14</v>
-      </c>
-      <c r="Z23">
+      <c r="AA23">
+        <v>14</v>
+      </c>
+      <c r="AB23">
         <v>363838</v>
       </c>
-      <c r="AA23" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB23" t="s">
-        <v>47</v>
-      </c>
       <c r="AC23" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="AD23" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="AE23" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="AF23" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG23">
+        <v>79</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI23">
         <v>-0.03344165279758522</v>
       </c>
-      <c r="AH23">
+      <c r="AJ23">
         <v>0.9671113378262057</v>
       </c>
-      <c r="AI23">
+      <c r="AK23">
         <v>0.9440322217607759</v>
       </c>
-      <c r="AJ23">
+      <c r="AL23">
         <v>0.9907546778514577</v>
       </c>
-      <c r="AK23" t="s">
-        <v>41</v>
-      </c>
-      <c r="AL23">
+      <c r="AM23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO23">
         <v>0.0003619438336894042</v>
       </c>
-      <c r="AM23">
+      <c r="AP23">
         <v>0.005067213671651659</v>
       </c>
-      <c r="AN23">
-        <v>14</v>
-      </c>
-      <c r="AO23">
+      <c r="AQ23">
+        <v>14</v>
+      </c>
+      <c r="AR23">
         <v>371359</v>
       </c>
-      <c r="AP23" t="s">
-        <v>46</v>
-      </c>
-      <c r="AQ23" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR23" t="s">
-        <v>49</v>
-      </c>
       <c r="AS23" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="AT23" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="AU23" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV23">
+        <v>69</v>
+      </c>
+      <c r="AV23" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW23" t="s">
+        <v>80</v>
+      </c>
+      <c r="AX23" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY23">
         <v>-0.03362247553437452</v>
       </c>
-      <c r="AW23">
+      <c r="AZ23">
         <v>0.9669364779171201</v>
       </c>
-      <c r="AX23">
+      <c r="BA23">
         <v>0.9439719414079509</v>
       </c>
-      <c r="AY23">
+      <c r="BB23">
         <v>0.9904596856260861</v>
       </c>
-      <c r="AZ23" t="s">
-        <v>41</v>
-      </c>
-      <c r="BA23">
+      <c r="BC23" t="s">
+        <v>42</v>
+      </c>
+      <c r="BD23" t="s">
+        <v>168</v>
+      </c>
+      <c r="BE23">
         <v>0.0003144270628968034</v>
       </c>
-      <c r="BB23">
+      <c r="BF23">
         <v>0.004401978880555248</v>
       </c>
-      <c r="BC23">
-        <v>14</v>
-      </c>
-      <c r="BD23">
+      <c r="BG23">
+        <v>14</v>
+      </c>
+      <c r="BH23">
         <v>374808</v>
       </c>
-      <c r="BE23" t="s">
-        <v>46</v>
-      </c>
-      <c r="BF23" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG23" t="s">
-        <v>49</v>
-      </c>
-      <c r="BH23" t="s">
-        <v>59</v>
-      </c>
       <c r="BI23" t="s">
-        <v>60</v>
+        <v>66</v>
+      </c>
+      <c r="BJ23" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK23" t="s">
+        <v>69</v>
+      </c>
+      <c r="BL23" t="s">
+        <v>79</v>
+      </c>
+      <c r="BM23" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B1:P1"/>
-    <mergeCell ref="Q1:AE1"/>
-    <mergeCell ref="AF1:AT1"/>
-    <mergeCell ref="AU1:BI1"/>
+    <mergeCell ref="B1:Q1"/>
+    <mergeCell ref="R1:AG1"/>
+    <mergeCell ref="AH1:AW1"/>
+    <mergeCell ref="AX1:BM1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4958,10 +5418,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:29">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -4970,35 +5430,39 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
-      <c r="Q1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
+      <c r="T1" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="U1" s="1"/>
-      <c r="V1" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="V1" s="1"/>
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
+      <c r="Z1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:29">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>4</v>
@@ -5007,850 +5471,982 @@
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>103</v>
+        <v>170</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="J2" s="1" t="s">
-        <v>103</v>
+        <v>10</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>104</v>
+        <v>170</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="P2" s="1" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="Q2" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="V2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="Z2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="W2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="X2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="AC2" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="3" spans="1:25" hidden="1"/>
-    <row r="4" spans="1:25">
+    <row r="3" spans="1:29" hidden="1"/>
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
+        <v>173</v>
+      </c>
+      <c r="F4" t="s">
+        <v>182</v>
+      </c>
+      <c r="G4" t="s">
+        <v>189</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
+        <v>82</v>
+      </c>
+      <c r="J4" t="s">
+        <v>97</v>
+      </c>
+      <c r="K4" t="s">
+        <v>199</v>
+      </c>
+      <c r="L4" t="s">
+        <v>208</v>
+      </c>
+      <c r="M4" t="s">
+        <v>216</v>
+      </c>
+      <c r="N4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4" t="s">
         <v>114</v>
       </c>
-      <c r="F4" t="s">
-        <v>121</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="P4" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>226</v>
+      </c>
+      <c r="R4" t="s">
+        <v>174</v>
+      </c>
+      <c r="S4" t="s">
+        <v>238</v>
+      </c>
+      <c r="T4" t="s">
+        <v>20</v>
+      </c>
+      <c r="U4" t="s">
+        <v>141</v>
+      </c>
+      <c r="V4" t="s">
+        <v>153</v>
+      </c>
+      <c r="W4" t="s">
+        <v>248</v>
+      </c>
+      <c r="X4" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>263</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA4" t="s">
         <v>62</v>
       </c>
-      <c r="I4" t="s">
-        <v>131</v>
-      </c>
-      <c r="J4" t="s">
-        <v>140</v>
-      </c>
-      <c r="K4" t="s">
-        <v>148</v>
-      </c>
-      <c r="L4" t="s">
-        <v>19</v>
-      </c>
-      <c r="M4" t="s">
-        <v>77</v>
-      </c>
-      <c r="N4" t="s">
-        <v>158</v>
-      </c>
-      <c r="O4" t="s">
-        <v>106</v>
-      </c>
-      <c r="P4" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>19</v>
-      </c>
-      <c r="R4" t="s">
-        <v>89</v>
-      </c>
-      <c r="S4" t="s">
-        <v>180</v>
-      </c>
-      <c r="T4" t="s">
-        <v>189</v>
-      </c>
-      <c r="U4" t="s">
-        <v>195</v>
-      </c>
-      <c r="V4" t="s">
-        <v>19</v>
-      </c>
-      <c r="W4" t="s">
-        <v>42</v>
-      </c>
-      <c r="X4" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>48</v>
+      <c r="AB4" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>115</v>
+        <v>174</v>
       </c>
       <c r="F5" t="s">
-        <v>122</v>
+        <v>183</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>190</v>
       </c>
       <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J5" t="s">
+        <v>98</v>
+      </c>
+      <c r="K5" t="s">
+        <v>200</v>
+      </c>
+      <c r="L5" t="s">
+        <v>209</v>
+      </c>
+      <c r="M5" t="s">
+        <v>217</v>
+      </c>
+      <c r="N5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" t="s">
+        <v>116</v>
+      </c>
+      <c r="P5" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>227</v>
+      </c>
+      <c r="R5" t="s">
+        <v>183</v>
+      </c>
+      <c r="S5" t="s">
+        <v>239</v>
+      </c>
+      <c r="T5" t="s">
+        <v>20</v>
+      </c>
+      <c r="U5" t="s">
+        <v>142</v>
+      </c>
+      <c r="V5" t="s">
+        <v>155</v>
+      </c>
+      <c r="W5" t="s">
+        <v>249</v>
+      </c>
+      <c r="X5" t="s">
+        <v>258</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>264</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA5" t="s">
         <v>63</v>
       </c>
-      <c r="I5" t="s">
-        <v>132</v>
-      </c>
-      <c r="J5" t="s">
-        <v>141</v>
-      </c>
-      <c r="K5" t="s">
-        <v>149</v>
-      </c>
-      <c r="L5" t="s">
-        <v>19</v>
-      </c>
-      <c r="M5" t="s">
-        <v>79</v>
-      </c>
-      <c r="N5" t="s">
-        <v>159</v>
-      </c>
-      <c r="O5" t="s">
-        <v>115</v>
-      </c>
-      <c r="P5" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>19</v>
-      </c>
-      <c r="R5" t="s">
-        <v>90</v>
-      </c>
-      <c r="S5" t="s">
-        <v>181</v>
-      </c>
-      <c r="T5" t="s">
-        <v>190</v>
-      </c>
-      <c r="U5" t="s">
-        <v>196</v>
-      </c>
-      <c r="V5" t="s">
-        <v>19</v>
-      </c>
-      <c r="W5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>48</v>
+      <c r="AB5" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
-        <v>116</v>
+        <v>175</v>
       </c>
       <c r="F6" t="s">
-        <v>123</v>
+        <v>184</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
       <c r="H6" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="I6" t="s">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="J6" t="s">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="K6" t="s">
-        <v>150</v>
+        <v>201</v>
       </c>
       <c r="L6" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="M6" t="s">
-        <v>80</v>
+        <v>218</v>
       </c>
       <c r="N6" t="s">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="O6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="P6" t="s">
-        <v>172</v>
+        <v>130</v>
       </c>
       <c r="Q6" t="s">
-        <v>19</v>
+        <v>228</v>
       </c>
       <c r="R6" t="s">
-        <v>92</v>
+        <v>183</v>
       </c>
       <c r="S6" t="s">
-        <v>182</v>
+        <v>240</v>
       </c>
       <c r="T6" t="s">
-        <v>191</v>
+        <v>20</v>
       </c>
       <c r="U6" t="s">
-        <v>197</v>
+        <v>144</v>
       </c>
       <c r="V6" t="s">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="W6" t="s">
-        <v>44</v>
+        <v>250</v>
       </c>
       <c r="X6" t="s">
-        <v>47</v>
+        <v>259</v>
       </c>
       <c r="Y6" t="s">
-        <v>48</v>
+        <v>265</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
-        <v>115</v>
+        <v>176</v>
       </c>
       <c r="F7" t="s">
-        <v>124</v>
+        <v>183</v>
       </c>
       <c r="G7" t="s">
-        <v>19</v>
+        <v>192</v>
       </c>
       <c r="H7" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="I7" t="s">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="J7" t="s">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="K7" t="s">
-        <v>151</v>
+        <v>202</v>
       </c>
       <c r="L7" t="s">
-        <v>19</v>
+        <v>211</v>
       </c>
       <c r="M7" t="s">
-        <v>28</v>
+        <v>219</v>
       </c>
       <c r="N7" t="s">
-        <v>161</v>
+        <v>20</v>
       </c>
       <c r="O7" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="P7" t="s">
-        <v>173</v>
+        <v>131</v>
       </c>
       <c r="Q7" t="s">
-        <v>19</v>
+        <v>229</v>
       </c>
       <c r="R7" t="s">
-        <v>93</v>
+        <v>183</v>
       </c>
       <c r="S7" t="s">
+        <v>241</v>
+      </c>
+      <c r="T7" t="s">
+        <v>20</v>
+      </c>
+      <c r="U7" t="s">
+        <v>145</v>
+      </c>
+      <c r="V7" t="s">
+        <v>158</v>
+      </c>
+      <c r="W7" t="s">
+        <v>251</v>
+      </c>
+      <c r="X7" t="s">
         <v>183</v>
       </c>
-      <c r="T7" t="s">
-        <v>115</v>
-      </c>
-      <c r="U7" t="s">
-        <v>198</v>
-      </c>
-      <c r="V7" t="s">
-        <v>19</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="s">
-        <v>47</v>
-      </c>
       <c r="Y7" t="s">
-        <v>48</v>
+        <v>266</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>65</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
-        <v>115</v>
+        <v>177</v>
       </c>
       <c r="F8" t="s">
-        <v>125</v>
+        <v>183</v>
       </c>
       <c r="G8" t="s">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="I8" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="J8" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="K8" t="s">
-        <v>152</v>
+        <v>203</v>
       </c>
       <c r="L8" t="s">
-        <v>19</v>
+        <v>183</v>
       </c>
       <c r="M8" t="s">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="N8" t="s">
-        <v>162</v>
+        <v>20</v>
       </c>
       <c r="O8" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="P8" t="s">
-        <v>174</v>
+        <v>132</v>
       </c>
       <c r="Q8" t="s">
-        <v>19</v>
+        <v>230</v>
       </c>
       <c r="R8" t="s">
-        <v>94</v>
+        <v>183</v>
       </c>
       <c r="S8" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="T8" t="s">
-        <v>115</v>
+        <v>20</v>
       </c>
       <c r="U8" t="s">
-        <v>199</v>
+        <v>146</v>
       </c>
       <c r="V8" t="s">
-        <v>19</v>
+        <v>160</v>
       </c>
       <c r="W8" t="s">
-        <v>46</v>
+        <v>252</v>
       </c>
       <c r="X8" t="s">
-        <v>47</v>
+        <v>183</v>
       </c>
       <c r="Y8" t="s">
-        <v>48</v>
+        <v>267</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="E9" t="s">
-        <v>117</v>
+        <v>178</v>
       </c>
       <c r="F9" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G9" t="s">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="H9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" t="s">
+        <v>89</v>
+      </c>
+      <c r="J9" t="s">
+        <v>106</v>
+      </c>
+      <c r="K9" t="s">
+        <v>204</v>
+      </c>
+      <c r="L9" t="s">
+        <v>212</v>
+      </c>
+      <c r="M9" t="s">
+        <v>221</v>
+      </c>
+      <c r="N9" t="s">
+        <v>22</v>
+      </c>
+      <c r="O9" t="s">
+        <v>120</v>
+      </c>
+      <c r="P9" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>231</v>
+      </c>
+      <c r="R9" t="s">
+        <v>236</v>
+      </c>
+      <c r="S9" t="s">
+        <v>243</v>
+      </c>
+      <c r="T9" t="s">
+        <v>22</v>
+      </c>
+      <c r="U9" t="s">
+        <v>147</v>
+      </c>
+      <c r="V9" t="s">
+        <v>161</v>
+      </c>
+      <c r="W9" t="s">
+        <v>204</v>
+      </c>
+      <c r="X9" t="s">
+        <v>212</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>268</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC9" t="s">
         <v>69</v>
       </c>
-      <c r="I9" t="s">
-        <v>136</v>
-      </c>
-      <c r="J9" t="s">
-        <v>144</v>
-      </c>
-      <c r="K9" t="s">
-        <v>153</v>
-      </c>
-      <c r="L9" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" t="s">
-        <v>83</v>
-      </c>
-      <c r="N9" t="s">
-        <v>163</v>
-      </c>
-      <c r="O9" t="s">
-        <v>168</v>
-      </c>
-      <c r="P9" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>21</v>
-      </c>
-      <c r="R9" t="s">
-        <v>95</v>
-      </c>
-      <c r="S9" t="s">
-        <v>136</v>
-      </c>
-      <c r="T9" t="s">
-        <v>144</v>
-      </c>
-      <c r="U9" t="s">
-        <v>200</v>
-      </c>
-      <c r="V9" t="s">
-        <v>21</v>
-      </c>
-      <c r="W9" t="s">
-        <v>42</v>
-      </c>
-      <c r="X9" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>49</v>
-      </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
-        <v>118</v>
+        <v>179</v>
       </c>
       <c r="F10" t="s">
-        <v>127</v>
+        <v>186</v>
       </c>
       <c r="G10" t="s">
-        <v>21</v>
+        <v>195</v>
       </c>
       <c r="H10" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="I10" t="s">
-        <v>137</v>
+        <v>91</v>
       </c>
       <c r="J10" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="K10" t="s">
-        <v>154</v>
+        <v>205</v>
       </c>
       <c r="L10" t="s">
-        <v>21</v>
+        <v>213</v>
       </c>
       <c r="M10" t="s">
-        <v>85</v>
+        <v>222</v>
       </c>
       <c r="N10" t="s">
-        <v>164</v>
+        <v>22</v>
       </c>
       <c r="O10" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="P10" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="Q10" t="s">
-        <v>21</v>
+        <v>232</v>
       </c>
       <c r="R10" t="s">
-        <v>96</v>
+        <v>237</v>
       </c>
       <c r="S10" t="s">
-        <v>185</v>
+        <v>244</v>
       </c>
       <c r="T10" t="s">
-        <v>192</v>
+        <v>22</v>
       </c>
       <c r="U10" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="V10" t="s">
-        <v>21</v>
+        <v>162</v>
       </c>
       <c r="W10" t="s">
-        <v>43</v>
+        <v>253</v>
       </c>
       <c r="X10" t="s">
-        <v>47</v>
+        <v>260</v>
       </c>
       <c r="Y10" t="s">
-        <v>49</v>
+        <v>269</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
-        <v>119</v>
+        <v>180</v>
       </c>
       <c r="F11" t="s">
-        <v>128</v>
+        <v>187</v>
       </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>196</v>
       </c>
       <c r="H11" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="I11" t="s">
+        <v>93</v>
+      </c>
+      <c r="J11" t="s">
+        <v>110</v>
+      </c>
+      <c r="K11" t="s">
+        <v>206</v>
+      </c>
+      <c r="L11" t="s">
+        <v>214</v>
+      </c>
+      <c r="M11" t="s">
+        <v>223</v>
+      </c>
+      <c r="N11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O11" t="s">
+        <v>123</v>
+      </c>
+      <c r="P11" t="s">
         <v>138</v>
       </c>
-      <c r="J11" t="s">
-        <v>146</v>
-      </c>
-      <c r="K11" t="s">
-        <v>155</v>
-      </c>
-      <c r="L11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" t="s">
-        <v>86</v>
-      </c>
-      <c r="N11" t="s">
-        <v>165</v>
-      </c>
-      <c r="O11" t="s">
-        <v>115</v>
-      </c>
-      <c r="P11" t="s">
-        <v>177</v>
-      </c>
       <c r="Q11" t="s">
-        <v>21</v>
+        <v>233</v>
       </c>
       <c r="R11" t="s">
-        <v>97</v>
+        <v>183</v>
       </c>
       <c r="S11" t="s">
-        <v>186</v>
+        <v>245</v>
       </c>
       <c r="T11" t="s">
-        <v>193</v>
+        <v>22</v>
       </c>
       <c r="U11" t="s">
-        <v>202</v>
+        <v>149</v>
       </c>
       <c r="V11" t="s">
-        <v>21</v>
+        <v>164</v>
       </c>
       <c r="W11" t="s">
-        <v>44</v>
+        <v>254</v>
       </c>
       <c r="X11" t="s">
-        <v>47</v>
+        <v>261</v>
       </c>
       <c r="Y11" t="s">
-        <v>49</v>
+        <v>270</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>105</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="F12" t="s">
-        <v>129</v>
+        <v>188</v>
       </c>
       <c r="G12" t="s">
-        <v>21</v>
+        <v>197</v>
       </c>
       <c r="H12" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="I12" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="J12" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="K12" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="L12" t="s">
-        <v>21</v>
+        <v>215</v>
       </c>
       <c r="M12" t="s">
-        <v>87</v>
+        <v>224</v>
       </c>
       <c r="N12" t="s">
-        <v>166</v>
+        <v>22</v>
       </c>
       <c r="O12" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="P12" t="s">
-        <v>178</v>
+        <v>139</v>
       </c>
       <c r="Q12" t="s">
-        <v>21</v>
+        <v>234</v>
       </c>
       <c r="R12" t="s">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="S12" t="s">
-        <v>187</v>
+        <v>246</v>
       </c>
       <c r="T12" t="s">
-        <v>194</v>
+        <v>22</v>
       </c>
       <c r="U12" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="V12" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="W12" t="s">
-        <v>45</v>
+        <v>255</v>
       </c>
       <c r="X12" t="s">
-        <v>47</v>
+        <v>262</v>
       </c>
       <c r="Y12" t="s">
-        <v>49</v>
+        <v>271</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>65</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:29">
       <c r="A13" s="1">
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" t="s">
+        <v>181</v>
+      </c>
+      <c r="F13" t="s">
+        <v>183</v>
+      </c>
+      <c r="G13" t="s">
+        <v>198</v>
+      </c>
+      <c r="H13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" t="s">
+        <v>96</v>
+      </c>
+      <c r="J13" t="s">
         <v>113</v>
       </c>
-      <c r="E13" t="s">
-        <v>115</v>
-      </c>
-      <c r="F13" t="s">
-        <v>130</v>
-      </c>
-      <c r="G13" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" t="s">
-        <v>76</v>
-      </c>
-      <c r="I13" t="s">
-        <v>139</v>
-      </c>
-      <c r="J13" t="s">
-        <v>115</v>
-      </c>
       <c r="K13" t="s">
-        <v>157</v>
+        <v>207</v>
       </c>
       <c r="L13" t="s">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="M13" t="s">
-        <v>88</v>
+        <v>225</v>
       </c>
       <c r="N13" t="s">
+        <v>22</v>
+      </c>
+      <c r="O13" t="s">
+        <v>125</v>
+      </c>
+      <c r="P13" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>235</v>
+      </c>
+      <c r="R13" t="s">
+        <v>183</v>
+      </c>
+      <c r="S13" t="s">
+        <v>247</v>
+      </c>
+      <c r="T13" t="s">
+        <v>22</v>
+      </c>
+      <c r="U13" t="s">
+        <v>152</v>
+      </c>
+      <c r="V13" t="s">
         <v>167</v>
       </c>
-      <c r="O13" t="s">
-        <v>115</v>
-      </c>
-      <c r="P13" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>21</v>
-      </c>
-      <c r="R13" t="s">
-        <v>100</v>
-      </c>
-      <c r="S13" t="s">
-        <v>188</v>
-      </c>
-      <c r="T13" t="s">
-        <v>115</v>
-      </c>
-      <c r="U13" t="s">
-        <v>204</v>
-      </c>
-      <c r="V13" t="s">
-        <v>21</v>
-      </c>
       <c r="W13" t="s">
-        <v>46</v>
+        <v>256</v>
       </c>
       <c r="X13" t="s">
-        <v>47</v>
+        <v>183</v>
       </c>
       <c r="Y13" t="s">
-        <v>49</v>
+        <v>272</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="L1:P1"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="V1:Y1"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:S1"/>
+    <mergeCell ref="T1:Y1"/>
+    <mergeCell ref="Z1:AC1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
